--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -511,28 +511,28 @@
         <v>2.706008009890701</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1780932924736928</v>
+        <v>0.1780932924736926</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9929689668472601</v>
+        <v>0.9929689668472599</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03566239416189191</v>
+        <v>0.03566239416189187</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007175281641882765</v>
+        <v>0.007175281641882734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007719950074056484</v>
+        <v>0.0007719950074052961</v>
       </c>
       <c r="J2" t="n">
-        <v>2.394597843492738e-05</v>
+        <v>2.394597843492736e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05847720748751445</v>
+        <v>0.05847720748751425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349365622658823</v>
+        <v>0.0002349365622658821</v>
       </c>
       <c r="M2" t="n">
         <v>1.432599989730353</v>
@@ -553,28 +553,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.697361362355053</v>
+        <v>2.697361362355055</v>
       </c>
       <c r="E3" t="n">
         <v>0.1768205809551257</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9903087563028564</v>
+        <v>0.9903087563028568</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03494476554569712</v>
+        <v>0.03494476554569708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007080116861346226</v>
+        <v>0.007080116861346191</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007004995303756405</v>
+        <v>0.0007004995303765771</v>
       </c>
       <c r="J3" t="n">
         <v>2.350036145124532e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05464827279031591</v>
+        <v>0.05464827279031587</v>
       </c>
       <c r="L3" t="n">
         <v>0.0002348801108878565</v>
@@ -598,31 +598,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.692078225118515</v>
+        <v>2.692078225118516</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17601201789749</v>
+        <v>0.1760120178974902</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9884524837229285</v>
+        <v>0.988452483722929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03331803035568808</v>
+        <v>0.0333180303556881</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006944467822133808</v>
+        <v>0.006944467822133828</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006753979506629409</v>
+        <v>0.0006753979506626061</v>
       </c>
       <c r="J4" t="n">
-        <v>2.318209564193791e-05</v>
+        <v>2.318209564193797e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05381789054968973</v>
+        <v>0.05381789054968984</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002347647013509868</v>
+        <v>0.0002347647013509866</v>
       </c>
       <c r="M4" t="n">
         <v>1.432599990022929</v>
@@ -649,25 +649,25 @@
         <v>0.1752534398441324</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9852610815958212</v>
+        <v>0.9852610815958205</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02999030026241247</v>
+        <v>0.02999030026241248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006837129168521929</v>
+        <v>0.006837129168521927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006136757154107986</v>
+        <v>0.0006136757154116659</v>
       </c>
       <c r="J5" t="n">
-        <v>2.299585149579127e-05</v>
+        <v>2.299585149579124e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05372120059339941</v>
+        <v>0.05372120059339932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002347303173188505</v>
+        <v>0.0002347303173188504</v>
       </c>
       <c r="M5" t="n">
         <v>1.432599990220732</v>
@@ -688,34 +688,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.620133653935315</v>
+        <v>2.620133653935317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672737020697676</v>
+        <v>0.1672737020697674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9708555118184944</v>
+        <v>0.9708555118184946</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009579472969610942</v>
+        <v>0.009579472969610944</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006159847126158313</v>
+        <v>0.006159847126158327</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002767224467077283</v>
+        <v>0.0002767224467125274</v>
       </c>
       <c r="J6" t="n">
         <v>2.091862937066631e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03313277992802287</v>
+        <v>0.03313277992802285</v>
       </c>
       <c r="L6" t="n">
         <v>0.0002347073275291475</v>
       </c>
       <c r="M6" t="n">
-        <v>1.432599991619654</v>
+        <v>1.432599991619651</v>
       </c>
     </row>
     <row r="7">
@@ -736,28 +736,28 @@
         <v>2.597519110351288</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636728518731685</v>
+        <v>0.1636728518731687</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9649987685818792</v>
+        <v>0.9649987685818789</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002822094926071254</v>
+        <v>0.002822094926071259</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005624863702515263</v>
+        <v>0.005624863702515259</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001513123084818843</v>
+        <v>0.0001513123084813068</v>
       </c>
       <c r="J7" t="n">
-        <v>1.960824023286368e-05</v>
+        <v>1.960824023286366e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02739523956802948</v>
+        <v>0.02739523956802942</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002343790212780716</v>
+        <v>0.0002343790212780715</v>
       </c>
       <c r="M7" t="n">
         <v>1.432599992129632</v>
@@ -781,28 +781,28 @@
         <v>2.587984265709649</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1618991438890858</v>
+        <v>0.1618991438890859</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9614587155740644</v>
+        <v>0.9614587155740638</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001097844344738775</v>
+        <v>0.001097844344738763</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005385663452816351</v>
+        <v>0.005385663452816359</v>
       </c>
       <c r="I8" t="n">
-        <v>6.80321758028241e-05</v>
+        <v>6.803217580299227e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.876659201712198e-05</v>
+        <v>1.876659201712201e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02522199173979859</v>
+        <v>0.02522199173979853</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000234115595307775</v>
+        <v>0.0002341155953077749</v>
       </c>
       <c r="M8" t="n">
         <v>1.432599992346017</v>
@@ -823,34 +823,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.677924632695115</v>
+        <v>2.677924632695114</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1742368626401197</v>
+        <v>0.1742368626401196</v>
       </c>
       <c r="F9" t="n">
-        <v>0.984981148901522</v>
+        <v>0.9849811489015222</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02874552361591244</v>
+        <v>0.02874552361591243</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006828133118718161</v>
+        <v>0.006828133118718166</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005570175837200272</v>
+        <v>0.0005570175837196057</v>
       </c>
       <c r="J9" t="n">
-        <v>2.289153866969132e-05</v>
+        <v>2.289153866969133e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04971823203443439</v>
+        <v>0.04971823203443441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002348329240112782</v>
+        <v>0.0002348329240112783</v>
       </c>
       <c r="M9" t="n">
-        <v>1.432599990338008</v>
+        <v>1.432599990338007</v>
       </c>
     </row>
     <row r="10">
@@ -871,28 +871,28 @@
         <v>2.636845786131814</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1689754325744339</v>
+        <v>0.168975432574434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9760507773250791</v>
+        <v>0.9760507773250797</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01298082692668557</v>
+        <v>0.01298082692668556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006265986661075032</v>
+        <v>0.006265986661075028</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000343170737963549</v>
+        <v>0.0003431707379633868</v>
       </c>
       <c r="J10" t="n">
-        <v>2.139452285257013e-05</v>
+        <v>2.139452285257009e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03937357249370858</v>
+        <v>0.03937357249370856</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002346336113925816</v>
+        <v>0.0002346336113925815</v>
       </c>
       <c r="M10" t="n">
         <v>1.432599991278623</v>
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.597217932218061</v>
+        <v>2.597217932218059</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1646952321262042</v>
+        <v>0.1646952321262041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9665055164240092</v>
+        <v>0.9665055164240086</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00198182857909017</v>
+        <v>0.001981828579090161</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005662860675727137</v>
+        <v>0.005662860675727147</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002120038589030011</v>
+        <v>0.0002120038589029575</v>
       </c>
       <c r="J11" t="n">
-        <v>1.967550545350044e-05</v>
+        <v>1.96755054535005e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02530632848182365</v>
+        <v>0.0253063284818236</v>
       </c>
       <c r="L11" t="n">
         <v>0.0002344944663335631</v>
       </c>
       <c r="M11" t="n">
-        <v>1.432599992100517</v>
+        <v>1.432599992100515</v>
       </c>
     </row>
   </sheetData>
@@ -1037,31 +1037,31 @@
         <v>1.989565906451694</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1780932924736928</v>
+        <v>0.1780932924736926</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4201944283241621</v>
+        <v>0.4201944283241618</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03566239416189191</v>
+        <v>0.03566239416189187</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007175281641882765</v>
+        <v>0.007175281641882734</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007719950074056484</v>
+        <v>0.0007719950074052961</v>
       </c>
       <c r="J2" t="n">
-        <v>2.394597843492738e-05</v>
+        <v>2.394597843492736e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05847720748751445</v>
+        <v>0.05847720748751425</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349365622658823</v>
+        <v>0.0002349365622658821</v>
       </c>
       <c r="M2" t="n">
-        <v>1.288932424814444</v>
+        <v>1.288932424814445</v>
       </c>
     </row>
     <row r="3">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.978211186898917</v>
+        <v>1.978211186898918</v>
       </c>
       <c r="E3" t="n">
         <v>0.1768205809551257</v>
@@ -1088,19 +1088,19 @@
         <v>0.4148261456974744</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03494476554569712</v>
+        <v>0.03494476554569708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007080116861346226</v>
+        <v>0.007080116861346191</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007004995303756405</v>
+        <v>0.0007004995303765771</v>
       </c>
       <c r="J3" t="n">
         <v>2.350036145124532e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05464827279031591</v>
+        <v>0.05464827279031587</v>
       </c>
       <c r="L3" t="n">
         <v>0.0002348801108878565</v>
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.96413308753661</v>
+        <v>1.964133087536611</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17601201789749</v>
+        <v>0.1760120178974902</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4041749107801645</v>
+        <v>0.404174910780165</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03331803035568808</v>
+        <v>0.0333180303556881</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006944467822133808</v>
+        <v>0.006944467822133828</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006753979506629409</v>
+        <v>0.0006753979506626061</v>
       </c>
       <c r="J4" t="n">
-        <v>2.318209564193791e-05</v>
+        <v>2.318209564193797e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05381789054968973</v>
+        <v>0.05381789054968984</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002347647013509868</v>
+        <v>0.0002347647013509866</v>
       </c>
       <c r="M4" t="n">
-        <v>1.288932425383788</v>
+        <v>1.288932425383789</v>
       </c>
     </row>
     <row r="5">
@@ -1178,25 +1178,25 @@
         <v>0.3830022013923652</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02999030026241247</v>
+        <v>0.02999030026241248</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006837129168521929</v>
+        <v>0.006837129168521927</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006136757154107986</v>
+        <v>0.0006136757154116659</v>
       </c>
       <c r="J5" t="n">
-        <v>2.299585149579127e-05</v>
+        <v>2.299585149579124e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05372120059339941</v>
+        <v>0.05372120059339932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002347303173188505</v>
+        <v>0.0002347303173188504</v>
       </c>
       <c r="M5" t="n">
-        <v>1.288932426014233</v>
+        <v>1.288932426014232</v>
       </c>
     </row>
     <row r="6">
@@ -1214,34 +1214,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.758039546909672</v>
+        <v>1.758039546909673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672737020697676</v>
+        <v>0.1672737020697674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2524289662042886</v>
+        <v>0.2524289662042885</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009579472969610942</v>
+        <v>0.009579472969610944</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006159847126158313</v>
+        <v>0.006159847126158327</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002767224467077283</v>
+        <v>0.0002767224467125274</v>
       </c>
       <c r="J6" t="n">
         <v>2.091862937066631e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03313277992802287</v>
+        <v>0.03313277992802285</v>
       </c>
       <c r="L6" t="n">
         <v>0.0002347073275291475</v>
       </c>
       <c r="M6" t="n">
-        <v>1.288932430208216</v>
+        <v>1.288932430208213</v>
       </c>
     </row>
     <row r="7">
@@ -1262,28 +1262,28 @@
         <v>1.697489544291927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636728518731685</v>
+        <v>0.1636728518731687</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2086367630212066</v>
+        <v>0.2086367630212067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002822094926071254</v>
+        <v>0.002822094926071259</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005624863702515263</v>
+        <v>0.005624863702515259</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001513123084818843</v>
+        <v>0.0001513123084813068</v>
       </c>
       <c r="J7" t="n">
-        <v>1.960824023286368e-05</v>
+        <v>1.960824023286366e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02739523956802948</v>
+        <v>0.02739523956802942</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002343790212780716</v>
+        <v>0.0002343790212780715</v>
       </c>
       <c r="M7" t="n">
         <v>1.288932431630943</v>
@@ -1307,28 +1307,28 @@
         <v>1.679816484006319</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1618991438890858</v>
+        <v>0.1618991438890859</v>
       </c>
       <c r="F8" t="n">
         <v>0.196958494173612</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001097844344738775</v>
+        <v>0.001097844344738763</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005385663452816351</v>
+        <v>0.005385663452816359</v>
       </c>
       <c r="I8" t="n">
-        <v>6.80321758028241e-05</v>
+        <v>6.803217580299227e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.876659201712198e-05</v>
+        <v>1.876659201712201e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02522199173979859</v>
+        <v>0.02522199173979853</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000234115595307775</v>
+        <v>0.0002341155953077749</v>
       </c>
       <c r="M8" t="n">
         <v>1.288932432043139</v>
@@ -1349,31 +1349,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.923870069285613</v>
+        <v>1.923870069285612</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1742368626401197</v>
+        <v>0.1742368626401196</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3745941495029534</v>
+        <v>0.3745941495029533</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02874552361591244</v>
+        <v>0.02874552361591243</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006828133118718161</v>
+        <v>0.006828133118718166</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005570175837200272</v>
+        <v>0.0005570175837196057</v>
       </c>
       <c r="J9" t="n">
-        <v>2.289153866969132e-05</v>
+        <v>2.289153866969133e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04971823203443439</v>
+        <v>0.04971823203443441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002348329240112782</v>
+        <v>0.0002348329240112783</v>
       </c>
       <c r="M9" t="n">
         <v>1.288932426327074</v>
@@ -1397,28 +1397,28 @@
         <v>1.791453194032336</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1689754325744339</v>
+        <v>0.168975432574434</v>
       </c>
       <c r="F10" t="n">
         <v>0.2743257470388896</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01298082692668557</v>
+        <v>0.01298082692668556</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006265986661075032</v>
+        <v>0.006265986661075028</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000343170737963549</v>
+        <v>0.0003431707379633868</v>
       </c>
       <c r="J10" t="n">
-        <v>2.139452285257013e-05</v>
+        <v>2.139452285257009e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03937357249370858</v>
+        <v>0.03937357249370856</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002346336113925816</v>
+        <v>0.0002346336113925815</v>
       </c>
       <c r="M10" t="n">
         <v>1.288932429465335</v>
@@ -1439,28 +1439,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.691273365073799</v>
+        <v>1.691273365073798</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1646952321262042</v>
+        <v>0.1646952321262041</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2042285096361147</v>
+        <v>0.2042285096361148</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00198182857909017</v>
+        <v>0.001981828579090161</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005662860675727137</v>
+        <v>0.005662860675727147</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002120038589030011</v>
+        <v>0.0002120038589029575</v>
       </c>
       <c r="J11" t="n">
-        <v>1.967550545350044e-05</v>
+        <v>1.96755054535005e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02530632848182365</v>
+        <v>0.0253063284818236</v>
       </c>
       <c r="L11" t="n">
         <v>0.0002344944663335631</v>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9553504935099851</v>
+        <v>0.9553504935099834</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003273658681615044</v>
+        <v>0.0003273658681615041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001356635219671602</v>
+        <v>0.0001356635219671601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04834646513160136</v>
+        <v>0.04834646513160123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4027520952634854</v>
+        <v>0.4027520952634852</v>
       </c>
       <c r="I2" t="n">
-        <v>2.944450246784683e-07</v>
+        <v>2.94445024678453e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4953516167859343</v>
+        <v>0.4953516167859322</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436992493810691</v>
+        <v>0.008436992493811357</v>
       </c>
     </row>
     <row r="3">
@@ -1589,28 +1589,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.902414305993905</v>
+        <v>0.9024143059939039</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003082283564827504</v>
+        <v>0.00030822835648275</v>
       </c>
       <c r="F3" t="n">
         <v>0.0001309144444625493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04518086496389823</v>
+        <v>0.04518086496389826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.394647579692224</v>
+        <v>0.3946475796922241</v>
       </c>
       <c r="I3" t="n">
-        <v>2.887232129260151e-07</v>
+        <v>2.887232129260016e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4537094369522599</v>
+        <v>0.4537094369522596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436992861364678</v>
+        <v>0.00843699286136379</v>
       </c>
     </row>
     <row r="4">
@@ -1628,25 +1628,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8411212068435041</v>
+        <v>0.8411212068435057</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003015098723325118</v>
+        <v>0.0003015098723325119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001266441675120467</v>
+        <v>0.0001266441675120469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04449434028587039</v>
+        <v>0.04449434028587046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3762760984270917</v>
+        <v>0.376276098427092</v>
       </c>
       <c r="I4" t="n">
-        <v>2.786224800171552e-07</v>
+        <v>2.786224800171603e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4114853421763624</v>
+        <v>0.4114853421763635</v>
       </c>
       <c r="K4" t="n">
         <v>0.008436993291855099</v>
@@ -1667,22 +1667,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7840436879428395</v>
+        <v>0.7840436879428393</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002922024799817145</v>
+        <v>0.0002922024799817137</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001176903444903149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04441440114716642</v>
+        <v>0.04441440114716634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3386944862264652</v>
+        <v>0.3386944862264651</v>
       </c>
       <c r="I5" t="n">
-        <v>2.705928278102137e-07</v>
+        <v>2.705928278102157e-07</v>
       </c>
       <c r="J5" t="n">
         <v>0.3920876433668622</v>
@@ -1709,25 +1709,25 @@
         <v>0.4516219471413262</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001711763025266869</v>
+        <v>0.0001711763025266872</v>
       </c>
       <c r="F6" t="n">
-        <v>5.349336338336296e-05</v>
+        <v>5.349336338336295e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02739277161696186</v>
+        <v>0.0273927716169619</v>
       </c>
       <c r="H6" t="n">
-        <v>0.108185468213838</v>
+        <v>0.1081854682138382</v>
       </c>
       <c r="I6" t="n">
-        <v>2.509911952282192e-07</v>
+        <v>2.509911952282323e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3073817897233219</v>
+        <v>0.3073817897233221</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00843699693009925</v>
+        <v>0.00843699693009875</v>
       </c>
     </row>
     <row r="7">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3049435002443067</v>
+        <v>0.3049435002443068</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001392637843274556</v>
       </c>
       <c r="F7" t="n">
-        <v>3.32975745953618e-05</v>
+        <v>3.329757459536182e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02264921755763372</v>
+        <v>0.0226492175576337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03187123779037238</v>
+        <v>0.03187123779037239</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938964378820229e-07</v>
+        <v>1.938964378820212e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2418132914827766</v>
+        <v>0.2418132914827777</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998158163289</v>
+        <v>0.008436998158162345</v>
       </c>
     </row>
     <row r="8">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2633741616726774</v>
+        <v>0.2633741616726762</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001268136752651771</v>
+        <v>0.0001268136752651773</v>
       </c>
       <c r="F8" t="n">
         <v>2.683441427055336e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02085246879235921</v>
+        <v>0.02085246879235927</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01239846960665351</v>
+        <v>0.01239846960665342</v>
       </c>
       <c r="I8" t="n">
-        <v>1.313381314772107e-07</v>
+        <v>1.3133813147719e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>0.221532445344409</v>
+        <v>0.2215324453444089</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998501588411</v>
+        <v>0.008436998501587412</v>
       </c>
     </row>
     <row r="9">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7849256336739197</v>
+        <v>0.7849256336739204</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002788608290815207</v>
+        <v>0.0002788608290815211</v>
       </c>
       <c r="F9" t="n">
         <v>0.0001134446468861539</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04110491719309385</v>
+        <v>0.04110491719309386</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3246366414211758</v>
+        <v>0.3246366414211757</v>
       </c>
       <c r="I9" t="n">
-        <v>2.797346495780788e-07</v>
+        <v>2.797346495781052e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4103544959571349</v>
+        <v>0.4103544959571346</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436993891898004</v>
+        <v>0.008436993891899114</v>
       </c>
     </row>
     <row r="10">
@@ -1862,28 +1862,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4964361061495565</v>
+        <v>0.4964361061495562</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002190130611853353</v>
+        <v>0.0002190130611853348</v>
       </c>
       <c r="F10" t="n">
-        <v>7.119924330083524e-05</v>
+        <v>7.119924330083512e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03255239317096485</v>
+        <v>0.03255239317096484</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1465985491395269</v>
+        <v>0.1465985491395266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.527877408564234e-07</v>
+        <v>2.527877408564025e-07</v>
       </c>
       <c r="J10" t="n">
         <v>0.3085577023136259</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436996433211774</v>
+        <v>0.008436996433211885</v>
       </c>
     </row>
     <row r="11">
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3113703044865835</v>
+        <v>0.3113703044865839</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001193015987215101</v>
+        <v>0.0001193015987215094</v>
       </c>
       <c r="F11" t="n">
-        <v>3.241086841599089e-05</v>
+        <v>3.241086841599081e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02092219481952109</v>
+        <v>0.02092219481952105</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02238171697217529</v>
+        <v>0.02238171697217518</v>
       </c>
       <c r="I11" t="n">
-        <v>2.21351203567005e-07</v>
+        <v>2.213512035670071e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2594774606844535</v>
+        <v>0.2594774606844548</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436998192092537</v>
+        <v>0.008436998192091816</v>
       </c>
     </row>
   </sheetData>
@@ -2006,28 +2006,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.268039716468294</v>
+        <v>1.268039716468293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003273658681615044</v>
+        <v>0.0003273658681615041</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001356635219671602</v>
+        <v>0.0001356635219671601</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04834646513160136</v>
+        <v>0.04834646513160123</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4027520952634854</v>
+        <v>0.4027520952634852</v>
       </c>
       <c r="I2" t="n">
-        <v>2.944450246784683e-07</v>
+        <v>2.94445024678453e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8080408414385816</v>
+        <v>0.8080408414385806</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436990799472133</v>
+        <v>0.008436990799472799</v>
       </c>
     </row>
     <row r="3">
@@ -2048,22 +2048,22 @@
         <v>1.133248574220077</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003082283564827504</v>
+        <v>0.00030822835648275</v>
       </c>
       <c r="F3" t="n">
         <v>0.0001309144444625493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04518086496389823</v>
+        <v>0.04518086496389826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.394647579692224</v>
+        <v>0.3946475796922241</v>
       </c>
       <c r="I3" t="n">
-        <v>2.887232129260151e-07</v>
+        <v>2.887232129260016e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6845437064292297</v>
+        <v>0.6845437064292296</v>
       </c>
       <c r="K3" t="n">
         <v>0.008436991610566436</v>
@@ -2087,25 +2087,25 @@
         <v>1.029622127229082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003015098723325118</v>
+        <v>0.0003015098723325119</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001266441675120467</v>
+        <v>0.0001266441675120469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04449434028587039</v>
+        <v>0.04449434028587046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3762760984270917</v>
+        <v>0.376276098427092</v>
       </c>
       <c r="I4" t="n">
-        <v>2.786224800171552e-07</v>
+        <v>2.786224800171603e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5999862635833514</v>
+        <v>0.5999862635833513</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436992270443922</v>
+        <v>0.008436992270443255</v>
       </c>
     </row>
     <row r="5">
@@ -2123,28 +2123,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9439510283295476</v>
+        <v>0.9439510283295469</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002922024799817145</v>
+        <v>0.0002922024799817137</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001176903444903149</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04441440114716642</v>
+        <v>0.04441440114716634</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3386944862264652</v>
+        <v>0.3386944862264651</v>
       </c>
       <c r="I5" t="n">
-        <v>2.705928278102137e-07</v>
+        <v>2.705928278102157e-07</v>
       </c>
       <c r="J5" t="n">
         <v>0.551994984620045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436992918571029</v>
+        <v>0.008436992918570585</v>
       </c>
     </row>
     <row r="6">
@@ -2162,28 +2162,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5877004668660283</v>
+        <v>0.5877004668660277</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001711763025266869</v>
+        <v>0.0001711763025266872</v>
       </c>
       <c r="F6" t="n">
-        <v>5.349336338336296e-05</v>
+        <v>5.349336338336295e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02739277161696186</v>
+        <v>0.0273927716169619</v>
       </c>
       <c r="H6" t="n">
-        <v>0.108185468213838</v>
+        <v>0.1081854682138382</v>
       </c>
       <c r="I6" t="n">
-        <v>2.509911952282192e-07</v>
+        <v>2.509911952282323e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4434603101853804</v>
+        <v>0.4434603101853801</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436996192742741</v>
+        <v>0.008436996192742297</v>
       </c>
     </row>
     <row r="7">
@@ -2201,28 +2201,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4096050428682844</v>
+        <v>0.4096050428682836</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001392637843274556</v>
       </c>
       <c r="F7" t="n">
-        <v>3.32975745953618e-05</v>
+        <v>3.329757459536182e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02264921755763372</v>
+        <v>0.0226492175576337</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03187123779037238</v>
+        <v>0.03187123779037239</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938964378820229e-07</v>
+        <v>1.938964378820212e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3464748346738724</v>
+        <v>0.3464748346738723</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436997591045214</v>
+        <v>0.008436997591044548</v>
       </c>
     </row>
     <row r="8">
@@ -2240,28 +2240,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3542538837001756</v>
+        <v>0.354253883700175</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001268136752651771</v>
+        <v>0.0001268136752651773</v>
       </c>
       <c r="F8" t="n">
         <v>2.683441427055336e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02085246879235921</v>
+        <v>0.02085246879235927</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01239846960665351</v>
+        <v>0.01239846960665342</v>
       </c>
       <c r="I8" t="n">
-        <v>1.313381314772107e-07</v>
+        <v>1.3133813147719e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>0.312412167864349</v>
+        <v>0.3124121678643487</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998009146712</v>
+        <v>0.008436998009146379</v>
       </c>
     </row>
     <row r="9">
@@ -2279,28 +2279,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.006032879990656</v>
+        <v>1.006032879990657</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002788608290815207</v>
+        <v>0.0002788608290815211</v>
       </c>
       <c r="F9" t="n">
         <v>0.0001134446468861539</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04110491719309385</v>
+        <v>0.04110491719309386</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3246366414211758</v>
+        <v>0.3246366414211757</v>
       </c>
       <c r="I9" t="n">
-        <v>2.797346495780788e-07</v>
+        <v>2.797346495781052e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6314617434719642</v>
+        <v>0.6314617434719647</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436992693805156</v>
+        <v>0.008436992693805379</v>
       </c>
     </row>
     <row r="10">
@@ -2318,28 +2318,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6597957721705101</v>
+        <v>0.6597957721705089</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002190130611853353</v>
+        <v>0.0002190130611853348</v>
       </c>
       <c r="F10" t="n">
-        <v>7.119924330083524e-05</v>
+        <v>7.119924330083512e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03255239317096485</v>
+        <v>0.03255239317096484</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1465985491395269</v>
+        <v>0.1465985491395266</v>
       </c>
       <c r="I10" t="n">
-        <v>2.527877408564234e-07</v>
+        <v>2.527877408564025e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4719173692197605</v>
+        <v>0.4719173692197591</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00843699554803079</v>
+        <v>0.008436995548031345</v>
       </c>
     </row>
     <row r="11">
@@ -2357,28 +2357,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.331457899125619</v>
+        <v>0.3314578991256165</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001193015987215101</v>
+        <v>0.0001193015987215094</v>
       </c>
       <c r="F11" t="n">
-        <v>3.241086841599089e-05</v>
+        <v>3.241086841599081e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02092219481952109</v>
+        <v>0.02092219481952105</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02238171697217529</v>
+        <v>0.02238171697217518</v>
       </c>
       <c r="I11" t="n">
-        <v>2.21351203567005e-07</v>
+        <v>2.213512035670071e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2795650554323349</v>
+        <v>0.2795650554323334</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436998083246661</v>
+        <v>0.008436998083245772</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -508,34 +508,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.706008009890701</v>
+        <v>2.697755753143283</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1780932924736926</v>
+        <v>0.1770046506426656</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9929689668472599</v>
+        <v>0.9906413026672412</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03566239416189187</v>
+        <v>0.03332028509091799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007175281641882734</v>
+        <v>0.007134522571586236</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007719950074052961</v>
+        <v>0.0007426560757673144</v>
       </c>
       <c r="J2" t="n">
-        <v>2.394597843492736e-05</v>
+        <v>2.366558390921168e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05847720748751425</v>
+        <v>0.05605377579863238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349365622658821</v>
+        <v>0.0002349047987132504</v>
       </c>
       <c r="M2" t="n">
-        <v>1.432599989730353</v>
+        <v>1.43259998991385</v>
       </c>
     </row>
     <row r="3">
@@ -553,34 +553,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.697361362355055</v>
+        <v>2.687292138134788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1768205809551257</v>
+        <v>0.1753652466821184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9903087563028568</v>
+        <v>0.9876707119331583</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03494476554569708</v>
+        <v>0.03207727081048767</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007080116861346191</v>
+        <v>0.006950845406861199</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007004995303765771</v>
+        <v>0.0006728322794243694</v>
       </c>
       <c r="J3" t="n">
-        <v>2.350036145124532e-05</v>
+        <v>2.292703187514291e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05464827279031587</v>
+        <v>0.05169753441829467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002348801108878565</v>
+        <v>0.0002347794527370768</v>
       </c>
       <c r="M3" t="n">
-        <v>1.432599989896997</v>
+        <v>1.432599990119831</v>
       </c>
     </row>
     <row r="4">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.692078225118516</v>
+        <v>2.68108482772379</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1760120178974902</v>
+        <v>0.1742297025430327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.988452483722929</v>
+        <v>0.985513198483894</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0333180303556881</v>
+        <v>0.0304196271611382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006944467822133828</v>
+        <v>0.006725871138007338</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006753979506626061</v>
+        <v>0.0006432079368330033</v>
       </c>
       <c r="J4" t="n">
-        <v>2.318209564193797e-05</v>
+        <v>2.238978961716151e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05381789054968984</v>
+        <v>0.05069627631781808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002347647013509866</v>
+        <v>0.0002345640871387253</v>
       </c>
       <c r="M4" t="n">
-        <v>1.432599990022929</v>
+        <v>1.432599990266311</v>
       </c>
     </row>
     <row r="5">
@@ -643,34 +643,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.684534543569245</v>
+        <v>2.674903125675851</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1752534398441324</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9852610815958205</v>
+        <v>0.9826184071732463</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02999030026241248</v>
+        <v>0.02768872593440495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006837129168521927</v>
+        <v>0.006597103534782505</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006136757154116659</v>
+        <v>0.0005832603437575183</v>
       </c>
       <c r="J5" t="n">
-        <v>2.299585149579124e-05</v>
+        <v>2.221023784335889e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05372120059339932</v>
+        <v>0.05108145198441424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002347303173188504</v>
+        <v>0.0002344813412966113</v>
       </c>
       <c r="M5" t="n">
-        <v>1.432599990220732</v>
+        <v>1.432599990435134</v>
       </c>
     </row>
     <row r="6">
@@ -688,34 +688,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.620133653935317</v>
+        <v>2.612449863941507</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672737020697674</v>
+        <v>0.165448788679351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9708555118184946</v>
+        <v>0.9685272857894484</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009579472969610944</v>
+        <v>0.008803216561351725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006159847126158327</v>
+        <v>0.005755797827749523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002767224467125274</v>
+        <v>0.0002593664518785657</v>
       </c>
       <c r="J6" t="n">
-        <v>2.091862937066631e-05</v>
+        <v>1.970247582360286e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03313277992802285</v>
+        <v>0.03080138859357326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002347073275291475</v>
+        <v>0.0002343257814860045</v>
       </c>
       <c r="M6" t="n">
-        <v>1.432599991619651</v>
+        <v>1.432599991780845</v>
       </c>
     </row>
     <row r="7">
@@ -733,34 +733,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.597519110351288</v>
+        <v>2.590125934180029</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636728518731687</v>
+        <v>0.1615019614938295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9649987685818789</v>
+        <v>0.9625373585235353</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002822094926071259</v>
+        <v>0.002664909953161935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005624863702515259</v>
+        <v>0.005183495819838593</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001513123084813068</v>
+        <v>0.0001351527580921877</v>
       </c>
       <c r="J7" t="n">
-        <v>1.960824023286366e-05</v>
+        <v>1.837741014355906e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02739523956802942</v>
+        <v>0.02525078206769121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002343790212780715</v>
+        <v>0.0002339038671066824</v>
       </c>
       <c r="M7" t="n">
-        <v>1.432599992129632</v>
+        <v>1.43259999228663</v>
       </c>
     </row>
     <row r="8">
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.587984265709649</v>
+        <v>2.581879576756648</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1618991438890859</v>
+        <v>0.1600401217258293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9614587155740638</v>
+        <v>0.9594933224300903</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001097844344738763</v>
+        <v>0.00100873894466173</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005385663452816359</v>
+        <v>0.004997759118034201</v>
       </c>
       <c r="I8" t="n">
-        <v>6.803217580299227e-05</v>
+        <v>5.141759203917151e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.876659201712201e-05</v>
+        <v>1.784742985847446e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02522199173979853</v>
+        <v>0.02343665449195835</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002341155953077749</v>
+        <v>0.0002337225489288063</v>
       </c>
       <c r="M8" t="n">
-        <v>1.432599992346017</v>
+        <v>1.432599992475247</v>
       </c>
     </row>
     <row r="9">
@@ -823,34 +823,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.677924632695114</v>
+        <v>2.666938767554188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1742368626401196</v>
+        <v>0.1724597851737661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9849811489015222</v>
+        <v>0.9820751158796159</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02874552361591243</v>
+        <v>0.02602822705092953</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006828133118718166</v>
+        <v>0.006535004021761003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005570175837196057</v>
+        <v>0.0005231448288668785</v>
       </c>
       <c r="J9" t="n">
-        <v>2.289153866969133e-05</v>
+        <v>2.211240974831632e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04971823203443441</v>
+        <v>0.04646075348385699</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002348329240112783</v>
+        <v>0.0002346341295683079</v>
       </c>
       <c r="M9" t="n">
-        <v>1.432599990338007</v>
+        <v>1.432599990576075</v>
       </c>
     </row>
     <row r="10">
@@ -868,34 +868,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.636845786131814</v>
+        <v>2.625473643986357</v>
       </c>
       <c r="E10" t="n">
-        <v>0.168975432574434</v>
+        <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9760507773250797</v>
+        <v>0.9727659338281381</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01298082692668556</v>
+        <v>0.01112061915572762</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006265986661075028</v>
+        <v>0.005847858327735188</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003431707379633868</v>
+        <v>0.0003082891040218845</v>
       </c>
       <c r="J10" t="n">
-        <v>2.139452285257009e-05</v>
+        <v>2.015830940726062e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03937357249370856</v>
+        <v>0.03596719112729574</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002346336113925815</v>
+        <v>0.0002342417742032933</v>
       </c>
       <c r="M10" t="n">
-        <v>1.432599991278623</v>
+        <v>1.432599991522813</v>
       </c>
     </row>
     <row r="11">
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.597217932218059</v>
+        <v>2.595516863958469</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1646952321262041</v>
+        <v>0.1627298041679663</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9665055164240086</v>
+        <v>0.9646725810266092</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001981828579090161</v>
+        <v>0.001916112446268599</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005662860675727147</v>
+        <v>0.005419358970709854</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002120038589029575</v>
+        <v>0.0001967717792873163</v>
       </c>
       <c r="J11" t="n">
-        <v>1.96755054535005e-05</v>
+        <v>1.895508401788367e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0253063284818236</v>
+        <v>0.02772923758671252</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002344944663335631</v>
+        <v>0.0002340507071139726</v>
       </c>
       <c r="M11" t="n">
-        <v>1.432599992100515</v>
+        <v>1.432599992189783</v>
       </c>
     </row>
   </sheetData>
@@ -1034,34 +1034,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.989565906451694</v>
+        <v>1.968528699246639</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1780932924736926</v>
+        <v>0.1770046506426656</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4201944283241618</v>
+        <v>0.4050818133788934</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03566239416189187</v>
+        <v>0.03332028509091799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007175281641882734</v>
+        <v>0.007134522571586236</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007719950074052961</v>
+        <v>0.0007426560757673144</v>
       </c>
       <c r="J2" t="n">
-        <v>2.394597843492736e-05</v>
+        <v>2.366558390921168e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05847720748751425</v>
+        <v>0.05605377579863238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349365622658821</v>
+        <v>0.0002349047987132504</v>
       </c>
       <c r="M2" t="n">
-        <v>1.288932424814445</v>
+        <v>1.288932425305554</v>
       </c>
     </row>
     <row r="3">
@@ -1079,34 +1079,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.978211186898918</v>
+        <v>1.952221978677433</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1768205809551257</v>
+        <v>0.1753652466821184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4148261456974744</v>
+        <v>0.3962681169435137</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03494476554569708</v>
+        <v>0.03207727081048767</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007080116861346191</v>
+        <v>0.006950845406861199</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007004995303765771</v>
+        <v>0.0006728322794243694</v>
       </c>
       <c r="J3" t="n">
-        <v>2.350036145124532e-05</v>
+        <v>2.292703187514291e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05464827279031587</v>
+        <v>0.05169753441829467</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002348801108878565</v>
+        <v>0.0002347794527370768</v>
       </c>
       <c r="M3" t="n">
-        <v>1.288932425046243</v>
+        <v>1.288932425652121</v>
       </c>
     </row>
     <row r="4">
@@ -1124,34 +1124,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.964133087536611</v>
+        <v>1.937127987001215</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1760120178974902</v>
+        <v>0.1742297025430327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.404174910780165</v>
+        <v>0.3852239220152078</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0333180303556881</v>
+        <v>0.0304196271611382</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006944467822133828</v>
+        <v>0.006725871138007338</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006753979506626061</v>
+        <v>0.0006432079368330033</v>
       </c>
       <c r="J4" t="n">
-        <v>2.318209564193797e-05</v>
+        <v>2.238978961716151e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05381789054968984</v>
+        <v>0.05069627631781808</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002347647013509866</v>
+        <v>0.0002345640871387253</v>
       </c>
       <c r="M4" t="n">
-        <v>1.288932425383789</v>
+        <v>1.288932426012422</v>
       </c>
     </row>
     <row r="5">
@@ -1169,34 +1169,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.93860809915929</v>
+        <v>1.916356514038503</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1752534398441324</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3830022013923652</v>
+        <v>0.3677393594387466</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02999030026241248</v>
+        <v>0.02768872593440495</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006837129168521927</v>
+        <v>0.006597103534782505</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0006136757154116659</v>
+        <v>0.0005832603437575183</v>
       </c>
       <c r="J5" t="n">
-        <v>2.299585149579124e-05</v>
+        <v>2.221023784335889e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05372120059339932</v>
+        <v>0.05108145198441424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002347303173188504</v>
+        <v>0.0002344813412966113</v>
       </c>
       <c r="M5" t="n">
-        <v>1.288932426014232</v>
+        <v>1.288932426532286</v>
       </c>
     </row>
     <row r="6">
@@ -1214,34 +1214,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.758039546909673</v>
+        <v>1.746729894688288</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1672737020697674</v>
+        <v>0.165448788679351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2524289662042885</v>
+        <v>0.2464748778604278</v>
       </c>
       <c r="G6" t="n">
-        <v>0.009579472969610944</v>
+        <v>0.008803216561351725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006159847126158327</v>
+        <v>0.005755797827749523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002767224467125274</v>
+        <v>0.0002593664518785657</v>
       </c>
       <c r="J6" t="n">
-        <v>2.091862937066631e-05</v>
+        <v>1.970247582360286e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03313277992802285</v>
+        <v>0.03080138859357326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002347073275291475</v>
+        <v>0.0002343257814860045</v>
       </c>
       <c r="M6" t="n">
-        <v>1.288932430208213</v>
+        <v>1.288932430456647</v>
       </c>
     </row>
     <row r="7">
@@ -1259,34 +1259,34 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.697489544291927</v>
+        <v>1.690153426011455</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1636728518731687</v>
+        <v>0.1615019614938295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2086367630212067</v>
+        <v>0.206232410855022</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002822094926071259</v>
+        <v>0.002664909953161935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005624863702515259</v>
+        <v>0.005183495819838593</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001513123084813068</v>
+        <v>0.0001351527580921877</v>
       </c>
       <c r="J7" t="n">
-        <v>1.960824023286366e-05</v>
+        <v>1.837741014355906e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02739523956802942</v>
+        <v>0.02525078206769121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002343790212780715</v>
+        <v>0.0002339038671066824</v>
       </c>
       <c r="M7" t="n">
-        <v>1.288932431630943</v>
+        <v>1.28893243178657</v>
       </c>
     </row>
     <row r="8">
@@ -1304,34 +1304,34 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.679816484006319</v>
+        <v>1.673886330969188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1618991438890859</v>
+        <v>0.1600401217258293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.196958494173612</v>
+        <v>0.1951676369497101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001097844344738763</v>
+        <v>0.00100873894466173</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005385663452816359</v>
+        <v>0.004997759118034201</v>
       </c>
       <c r="I8" t="n">
-        <v>6.803217580299227e-05</v>
+        <v>5.141759203917151e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.876659201712201e-05</v>
+        <v>1.784742985847446e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02522199173979853</v>
+        <v>0.02343665449195835</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002341155953077749</v>
+        <v>0.0002337225489288063</v>
       </c>
       <c r="M8" t="n">
-        <v>1.288932432043139</v>
+        <v>1.288932432168167</v>
       </c>
     </row>
     <row r="9">
@@ -1349,34 +1349,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.923870069285612</v>
+        <v>1.897980047276503</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1742368626401196</v>
+        <v>0.1724597851737661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3745941495029533</v>
+        <v>0.3567839592542623</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02874552361591243</v>
+        <v>0.02602822705092953</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006828133118718166</v>
+        <v>0.006535004021761003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005570175837196057</v>
+        <v>0.0005231448288668785</v>
       </c>
       <c r="J9" t="n">
-        <v>2.289153866969133e-05</v>
+        <v>2.211240974831632e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04971823203443441</v>
+        <v>0.04646075348385699</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002348329240112783</v>
+        <v>0.0002346341295683079</v>
       </c>
       <c r="M9" t="n">
-        <v>1.288932426327074</v>
+        <v>1.288932426923744</v>
       </c>
     </row>
     <row r="10">
@@ -1394,34 +1394,34 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.791453194032336</v>
+        <v>1.770432118235289</v>
       </c>
       <c r="E10" t="n">
-        <v>0.168975432574434</v>
+        <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2743257470388896</v>
+        <v>0.2613919696581965</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01298082692668556</v>
+        <v>0.01112061915572762</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006265986661075028</v>
+        <v>0.005847858327735188</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003431707379633868</v>
+        <v>0.0003082891040218845</v>
       </c>
       <c r="J10" t="n">
-        <v>2.139452285257009e-05</v>
+        <v>2.015830940726062e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03937357249370856</v>
+        <v>0.03596719112729574</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002346336113925815</v>
+        <v>0.0002342417742032933</v>
       </c>
       <c r="M10" t="n">
-        <v>1.288932429465335</v>
+        <v>1.288932429941687</v>
       </c>
     </row>
     <row r="11">
@@ -1439,34 +1439,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.691273365073798</v>
+        <v>1.68970516356903</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1646952321262041</v>
+        <v>0.1627298041679663</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2042285096361148</v>
+        <v>0.2025284409967362</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001981828579090161</v>
+        <v>0.001916112446268599</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005662860675727147</v>
+        <v>0.005419358970709854</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0002120038589029575</v>
+        <v>0.0001967717792873163</v>
       </c>
       <c r="J11" t="n">
-        <v>1.96755054535005e-05</v>
+        <v>1.895508401788367e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0253063284818236</v>
+        <v>0.02772923758671252</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002344944663335631</v>
+        <v>0.0002340507071139726</v>
       </c>
       <c r="M11" t="n">
-        <v>1.288932431744148</v>
+        <v>1.288932431830218</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9553504935099834</v>
+        <v>0.8537556471123281</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003273658681615041</v>
+        <v>0.0003092361873368597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001356635219671601</v>
+        <v>0.0001274586581092431</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04834646513160123</v>
+        <v>0.04634287500342411</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4027520952634852</v>
+        <v>0.3763015622064995</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94445024678453e-07</v>
+        <v>2.87180036450661e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4953516167859322</v>
+        <v>0.4222372346777837</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436992493811357</v>
+        <v>0.008436993199138265</v>
       </c>
     </row>
     <row r="3">
@@ -1589,28 +1589,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9024143059939039</v>
+        <v>0.7925894383766168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00030822835648275</v>
+        <v>0.0002878884378641578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001309144444625493</v>
+        <v>0.0001211983546970557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04518086496389826</v>
+        <v>0.04274132012335732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3946475796922241</v>
+        <v>0.3622636206254295</v>
       </c>
       <c r="I3" t="n">
-        <v>2.887232129260016e-07</v>
+        <v>2.658305254751579e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4537094369522596</v>
+        <v>0.3787381513588891</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00843699286136379</v>
+        <v>0.008436993645854152</v>
       </c>
     </row>
     <row r="4">
@@ -1628,28 +1628,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8411212068435057</v>
+        <v>0.7358395778613147</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003015098723325119</v>
+        <v>0.0002813057792045909</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001266441675120469</v>
+        <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04449434028587046</v>
+        <v>0.04191352256047335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.376276098427092</v>
+        <v>0.3435430756742123</v>
       </c>
       <c r="I4" t="n">
-        <v>2.786224800171603e-07</v>
+        <v>2.286927242425258e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4114853421763635</v>
+        <v>0.3415478593147119</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436993291855099</v>
+        <v>0.008436994055264102</v>
       </c>
     </row>
     <row r="5">
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7840436879428393</v>
+        <v>0.6976469345594718</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002922024799817137</v>
+        <v>0.000275539667712255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001176903444903149</v>
+        <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04441440114716634</v>
+        <v>0.04223196940044283</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3386944862264651</v>
+        <v>0.3127017309784114</v>
       </c>
       <c r="I5" t="n">
-        <v>2.705928278102157e-07</v>
+        <v>2.075700053810034e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3920876433668622</v>
+        <v>0.3338910652886802</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00843699378504581</v>
+        <v>0.008436994408128173</v>
       </c>
     </row>
     <row r="6">
@@ -1706,28 +1706,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4516219471413262</v>
+        <v>0.4042680512618932</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001711763025266872</v>
+        <v>0.0001615158763762971</v>
       </c>
       <c r="F6" t="n">
-        <v>5.349336338336295e-05</v>
+        <v>4.955266986951886e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0273927716169619</v>
+        <v>0.02546527653465741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1081854682138382</v>
+        <v>0.0994188415687266</v>
       </c>
       <c r="I6" t="n">
-        <v>2.509911952282323e-07</v>
+        <v>1.67630390188655e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3073817897233221</v>
+        <v>0.2707356997273885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00843699693009875</v>
+        <v>0.008436997254484657</v>
       </c>
     </row>
     <row r="7">
@@ -1745,28 +1745,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3049435002443068</v>
+        <v>0.2769355120041206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001392637843274556</v>
+        <v>0.0001327255374027533</v>
       </c>
       <c r="F7" t="n">
-        <v>3.329757459536182e-05</v>
+        <v>3.12911805157343e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0226492175576337</v>
+        <v>0.02087627140953937</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03187123779037239</v>
+        <v>0.03009607438166323</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938964378820212e-07</v>
+        <v>7.979581528031507e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2418132914827777</v>
+        <v>0.2173620713574961</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998158162345</v>
+        <v>0.008436998341688207</v>
       </c>
     </row>
     <row r="8">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2633741616726762</v>
+        <v>0.2424674618526513</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001268136752651773</v>
+        <v>0.0001216429948959389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.683441427055336e-05</v>
+        <v>2.540593178078801e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02085246879235927</v>
+        <v>0.01937642797732396</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01239846960665342</v>
+        <v>0.01139216065225714</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3133813147719e-07</v>
+        <v>3.444042669698768e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2215324453444089</v>
+        <v>0.2031147912169418</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998501587412</v>
+        <v>0.008436998639025028</v>
       </c>
     </row>
     <row r="9">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7849256336739204</v>
+        <v>0.6857950294355106</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002788608290815211</v>
+        <v>0.0002582399815828589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001134446468861539</v>
+        <v>0.0001037243484913611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04110491719309386</v>
+        <v>0.03841177263423207</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3246366414211757</v>
+        <v>0.2939489405329222</v>
       </c>
       <c r="I9" t="n">
-        <v>2.797346495781052e-07</v>
+        <v>2.352387166130046e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4103544959571346</v>
+        <v>0.3446351220860778</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436993891899114</v>
+        <v>0.008436994613487681</v>
       </c>
     </row>
     <row r="10">
@@ -1862,28 +1862,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4964361061495562</v>
+        <v>0.431730817717637</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002190130611853348</v>
+        <v>0.0002006880166748547</v>
       </c>
       <c r="F10" t="n">
-        <v>7.119924330083512e-05</v>
+        <v>6.324602195601301e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03255239317096484</v>
+        <v>0.02973614210440395</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1465985491395266</v>
+        <v>0.1255903528311782</v>
       </c>
       <c r="I10" t="n">
-        <v>2.527877408564025e-07</v>
+        <v>1.567269304237358e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3085577023136259</v>
+        <v>0.2677032350937341</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436996433211885</v>
+        <v>0.00843699692275951</v>
       </c>
     </row>
     <row r="11">
@@ -1901,28 +1901,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3113703044865839</v>
+        <v>0.2858980513713267</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001193015987215094</v>
+        <v>0.0001403214666166645</v>
       </c>
       <c r="F11" t="n">
-        <v>3.241086841599081e-05</v>
+        <v>3.125804518334548e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02092219481952105</v>
+        <v>0.02292535289750496</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02238171697217518</v>
+        <v>0.02163955395119727</v>
       </c>
       <c r="I11" t="n">
-        <v>2.213512035670071e-07</v>
+        <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2594774606844548</v>
+        <v>0.2327244551954743</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436998192091816</v>
+        <v>0.008436998307552734</v>
       </c>
     </row>
   </sheetData>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 30 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -2006,28 +2006,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.268039716468293</v>
+        <v>1.146704692771251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003273658681615041</v>
+        <v>0.0003092361873368597</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001356635219671601</v>
+        <v>0.0001274586581092431</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04834646513160123</v>
+        <v>0.04634287500342411</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4027520952634852</v>
+        <v>0.3763015622064995</v>
       </c>
       <c r="I2" t="n">
-        <v>2.94445024678453e-07</v>
+        <v>2.87180036450661e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8080408414385806</v>
+        <v>0.7151862819240815</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436990799472799</v>
+        <v>0.008436991611763034</v>
       </c>
     </row>
     <row r="3">
@@ -2045,28 +2045,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.133248574220077</v>
+        <v>1.005200607422688</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00030822835648275</v>
+        <v>0.0002878884378641578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001309144444625493</v>
+        <v>0.0001211983546970557</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04518086496389826</v>
+        <v>0.04274132012335732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3946475796922241</v>
+        <v>0.3622636206254295</v>
       </c>
       <c r="I3" t="n">
-        <v>2.887232129260016e-07</v>
+        <v>2.658305254751579e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6845437064292296</v>
+        <v>0.5913493215570135</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436991610566436</v>
+        <v>0.008436992493800588</v>
       </c>
     </row>
     <row r="4">
@@ -2084,28 +2084,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.029622127229082</v>
+        <v>0.9083785276337034</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0003015098723325119</v>
+        <v>0.0002813057792045909</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001266441675120469</v>
+        <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04449434028587046</v>
+        <v>0.04191352256047335</v>
       </c>
       <c r="H4" t="n">
-        <v>0.376276098427092</v>
+        <v>0.3435430756742123</v>
       </c>
       <c r="I4" t="n">
-        <v>2.786224800171603e-07</v>
+        <v>2.286927242425258e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5999862635833513</v>
+        <v>0.5140868100220199</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436992270443255</v>
+        <v>0.008436993120344849</v>
       </c>
     </row>
     <row r="5">
@@ -2123,28 +2123,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9439510283295469</v>
+        <v>0.8457793535109446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002922024799817137</v>
+        <v>0.000275539667712255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001176903444903149</v>
+        <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04441440114716634</v>
+        <v>0.04223196940044283</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3386944862264651</v>
+        <v>0.3127017309784114</v>
       </c>
       <c r="I5" t="n">
-        <v>2.705928278102157e-07</v>
+        <v>2.075700053810034e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.551994984620045</v>
+        <v>0.4820234850428252</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436992918570585</v>
+        <v>0.008436993605456022</v>
       </c>
     </row>
     <row r="6">
@@ -2162,28 +2162,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5877004668660277</v>
+        <v>0.537468974566251</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001711763025266872</v>
+        <v>0.0001615158763762971</v>
       </c>
       <c r="F6" t="n">
-        <v>5.349336338336295e-05</v>
+        <v>4.955266986951886e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0273927716169619</v>
+        <v>0.02546527653465741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1081854682138382</v>
+        <v>0.0994188415687266</v>
       </c>
       <c r="I6" t="n">
-        <v>2.509911952282323e-07</v>
+        <v>1.67630390188655e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4434603101853801</v>
+        <v>0.403936623753513</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436996192742297</v>
+        <v>0.008436996532718011</v>
       </c>
     </row>
     <row r="7">
@@ -2201,28 +2201,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4096050428682836</v>
+        <v>0.3826245304114747</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001392637843274556</v>
+        <v>0.0001327255374027533</v>
       </c>
       <c r="F7" t="n">
-        <v>3.329757459536182e-05</v>
+        <v>3.12911805157343e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0226492175576337</v>
+        <v>0.02087627140953937</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03187123779037239</v>
+        <v>0.03009607438166323</v>
       </c>
       <c r="I7" t="n">
-        <v>1.938964378820212e-07</v>
+        <v>7.979581528031507e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3464748346738723</v>
+        <v>0.3230510903375374</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436997591044548</v>
+        <v>0.00843699776900092</v>
       </c>
     </row>
     <row r="8">
@@ -2240,28 +2240,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.354253883700175</v>
+        <v>0.3345958313526998</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001268136752651773</v>
+        <v>0.0001216429948959389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.683441427055336e-05</v>
+        <v>2.540593178078801e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02085246879235927</v>
+        <v>0.01937642797732396</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01239846960665342</v>
+        <v>0.01139216065225714</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3133813147719e-07</v>
+        <v>3.444042669698768e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3124121678643487</v>
+        <v>0.2952431612161974</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998009146379</v>
+        <v>0.008436998139817908</v>
       </c>
     </row>
     <row r="9">
@@ -2279,28 +2279,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.006032879990657</v>
+        <v>0.8897190975905908</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002788608290815211</v>
+        <v>0.0002582399815828589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001134446468861539</v>
+        <v>0.0001037243484913611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04110491719309386</v>
+        <v>0.03841177263423207</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3246366414211757</v>
+        <v>0.2939489405329222</v>
       </c>
       <c r="I9" t="n">
-        <v>2.797346495781052e-07</v>
+        <v>2.352387166130046e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6314617434719647</v>
+        <v>0.5485591913461401</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436992693805379</v>
+        <v>0.008436993508505575</v>
       </c>
     </row>
     <row r="10">
@@ -2318,28 +2318,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6597957721705089</v>
+        <v>0.5828353310743951</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002190130611853348</v>
+        <v>0.0002006880166748547</v>
       </c>
       <c r="F10" t="n">
-        <v>7.119924330083512e-05</v>
+        <v>6.324602195601301e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.03255239317096484</v>
+        <v>0.02973614210440395</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1465985491395266</v>
+        <v>0.1255903528311782</v>
       </c>
       <c r="I10" t="n">
-        <v>2.527877408564025e-07</v>
+        <v>1.567269304237358e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4719173692197591</v>
+        <v>0.4188077492692678</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436995548031345</v>
+        <v>0.008436996103983851</v>
       </c>
     </row>
     <row r="11">
@@ -2357,28 +2357,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3314578991256165</v>
+        <v>0.3788320991683782</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001193015987215094</v>
+        <v>0.0001403214666166645</v>
       </c>
       <c r="F11" t="n">
-        <v>3.241086841599081e-05</v>
+        <v>3.125804518334548e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02092219481952105</v>
+        <v>0.02292535289750496</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02238171697217518</v>
+        <v>0.02163955395119727</v>
       </c>
       <c r="I11" t="n">
-        <v>2.213512035670071e-07</v>
+        <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2795650554323334</v>
+        <v>0.3256585034960959</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436998083245772</v>
+        <v>0.00843699780398266</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.68108482772379</v>
+        <v>2.681084827723792</v>
       </c>
       <c r="E4" t="n">
         <v>0.1742297025430327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.985513198483894</v>
+        <v>0.9855131984838948</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0304196271611382</v>
+        <v>0.03041962716113818</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006725871138007338</v>
+        <v>0.006725871138007352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006432079368330033</v>
+        <v>0.00064320793683306</v>
       </c>
       <c r="J4" t="n">
-        <v>2.238978961716151e-05</v>
+        <v>2.238978961716152e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05069627631781808</v>
+        <v>0.05069627631781804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002345640871387253</v>
+        <v>0.0002345640871387255</v>
       </c>
       <c r="M4" t="n">
-        <v>1.432599990266311</v>
+        <v>1.432599990266312</v>
       </c>
     </row>
     <row r="5">
@@ -643,31 +643,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.674903125675851</v>
+        <v>2.67490312567585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909713</v>
+        <v>0.1734774946909712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9826184071732463</v>
+        <v>0.9826184071732462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02768872593440495</v>
+        <v>0.02768872593440493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006597103534782505</v>
+        <v>0.006597103534782493</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005832603437575183</v>
+        <v>0.0005832603437571993</v>
       </c>
       <c r="J5" t="n">
-        <v>2.221023784335889e-05</v>
+        <v>2.221023784335904e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05108145198441424</v>
+        <v>0.05108145198441414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002344813412966113</v>
+        <v>0.000234481341296611</v>
       </c>
       <c r="M5" t="n">
         <v>1.432599990435134</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.937127987001215</v>
+        <v>1.937127987001214</v>
       </c>
       <c r="E4" t="n">
         <v>0.1742297025430327</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3852239220152078</v>
+        <v>0.3852239220152076</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0304196271611382</v>
+        <v>0.03041962716113818</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006725871138007338</v>
+        <v>0.006725871138007352</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006432079368330033</v>
+        <v>0.00064320793683306</v>
       </c>
       <c r="J4" t="n">
-        <v>2.238978961716151e-05</v>
+        <v>2.238978961716152e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05069627631781808</v>
+        <v>0.05069627631781804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002345640871387253</v>
+        <v>0.0002345640871387255</v>
       </c>
       <c r="M4" t="n">
         <v>1.288932426012422</v>
@@ -1169,31 +1169,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.916356514038503</v>
+        <v>1.916356514038502</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909713</v>
+        <v>0.1734774946909712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3677393594387466</v>
+        <v>0.3677393594387464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02768872593440495</v>
+        <v>0.02768872593440493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006597103534782505</v>
+        <v>0.006597103534782493</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005832603437575183</v>
+        <v>0.0005832603437571993</v>
       </c>
       <c r="J5" t="n">
-        <v>2.221023784335889e-05</v>
+        <v>2.221023784335904e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05108145198441424</v>
+        <v>0.05108145198441414</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002344813412966113</v>
+        <v>0.000234481341296611</v>
       </c>
       <c r="M5" t="n">
         <v>1.288932426532286</v>
@@ -1628,28 +1628,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7358395778613147</v>
+        <v>0.7358395778613145</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045909</v>
+        <v>0.0002813057792045913</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001165917847242302</v>
+        <v>0.0001165917847242303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047335</v>
+        <v>0.04191352256047336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3435430756742123</v>
+        <v>0.343543075674212</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425258e-07</v>
+        <v>2.286927242425216e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3415478593147119</v>
+        <v>0.3415478593147128</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436994055264102</v>
+        <v>0.008436994055263325</v>
       </c>
     </row>
     <row r="5">
@@ -1667,28 +1667,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6976469345594718</v>
+        <v>0.69764693455947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000275539667712255</v>
+        <v>0.0002755396677122543</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044283</v>
+        <v>0.04223196940044274</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784114</v>
+        <v>0.3127017309784111</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810034e-07</v>
+        <v>2.075700053810023e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3338910652886802</v>
+        <v>0.33389106528868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436994408128173</v>
+        <v>0.008436994408126841</v>
       </c>
     </row>
     <row r="6">
@@ -1748,7 +1748,7 @@
         <v>0.2769355120041206</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001327255374027533</v>
+        <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
         <v>3.12911805157343e-05</v>
@@ -1766,7 +1766,7 @@
         <v>0.2173620713574961</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998341688207</v>
+        <v>0.008436998341688151</v>
       </c>
     </row>
     <row r="8">
@@ -2084,28 +2084,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9083785276337034</v>
+        <v>0.9083785276337037</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045909</v>
+        <v>0.0002813057792045913</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001165917847242302</v>
+        <v>0.0001165917847242303</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047335</v>
+        <v>0.04191352256047336</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3435430756742123</v>
+        <v>0.343543075674212</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425258e-07</v>
+        <v>2.286927242425216e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5140868100220199</v>
+        <v>0.5140868100220193</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436993120344849</v>
+        <v>0.00843699312034607</v>
       </c>
     </row>
     <row r="5">
@@ -2123,28 +2123,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8457793535109446</v>
+        <v>0.8457793535109432</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000275539667712255</v>
+        <v>0.0002755396677122543</v>
       </c>
       <c r="F5" t="n">
         <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044283</v>
+        <v>0.04223196940044274</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784114</v>
+        <v>0.3127017309784111</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810034e-07</v>
+        <v>2.075700053810023e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4820234850428252</v>
+        <v>0.4820234850428222</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436993605456022</v>
+        <v>0.008436993605457799</v>
       </c>
     </row>
     <row r="6">
@@ -2204,7 +2204,7 @@
         <v>0.3826245304114747</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001327255374027533</v>
+        <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
         <v>3.12911805157343e-05</v>
@@ -2222,7 +2222,7 @@
         <v>0.3230510903375374</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00843699776900092</v>
+        <v>0.008436997769000865</v>
       </c>
     </row>
     <row r="8">

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -508,34 +508,34 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.697755753143283</v>
+        <v>2.697755753143285</v>
       </c>
       <c r="E2" t="n">
         <v>0.1770046506426656</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906413026672412</v>
+        <v>0.9906413026672419</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03332028509091799</v>
+        <v>0.033320285090918</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007134522571586236</v>
+        <v>0.007134522571586243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007426560757673144</v>
+        <v>0.0007426560757672062</v>
       </c>
       <c r="J2" t="n">
-        <v>2.366558390921168e-05</v>
+        <v>2.366558390921172e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05605377579863238</v>
+        <v>0.05605377579863243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349047987132504</v>
+        <v>0.0002349047987132502</v>
       </c>
       <c r="M2" t="n">
-        <v>1.43259998991385</v>
+        <v>1.432599989913851</v>
       </c>
     </row>
     <row r="3">
@@ -556,31 +556,31 @@
         <v>2.687292138134788</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1753652466821184</v>
+        <v>0.1753652466821185</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9876707119331583</v>
+        <v>0.9876707119331578</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03207727081048767</v>
+        <v>0.03207727081048773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006950845406861199</v>
+        <v>0.006950845406861223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006728322794243694</v>
+        <v>0.0006728322794234023</v>
       </c>
       <c r="J3" t="n">
-        <v>2.292703187514291e-05</v>
+        <v>2.292703187514303e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05169753441829467</v>
+        <v>0.05169753441829482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002347794527370768</v>
+        <v>0.0002347794527370767</v>
       </c>
       <c r="M3" t="n">
-        <v>1.432599990119831</v>
+        <v>1.432599990119832</v>
       </c>
     </row>
     <row r="4">
@@ -598,34 +598,34 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.681084827723792</v>
+        <v>2.681084827723789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1742297025430327</v>
+        <v>0.1742297025430324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9855131984838948</v>
+        <v>0.9855131984838945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03041962716113818</v>
+        <v>0.03041962716113816</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006725871138007352</v>
+        <v>0.006725871138007343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00064320793683306</v>
+        <v>0.0006432079368323447</v>
       </c>
       <c r="J4" t="n">
-        <v>2.238978961716152e-05</v>
+        <v>2.23897896171615e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05069627631781804</v>
+        <v>0.05069627631781801</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002345640871387255</v>
+        <v>0.0002345640871387254</v>
       </c>
       <c r="M4" t="n">
-        <v>1.432599990266312</v>
+        <v>1.432599990266311</v>
       </c>
     </row>
     <row r="5">
@@ -646,28 +646,28 @@
         <v>2.67490312567585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909712</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9826184071732462</v>
+        <v>0.9826184071732459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02768872593440493</v>
+        <v>0.02768872593440492</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006597103534782493</v>
+        <v>0.006597103534782496</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005832603437571993</v>
+        <v>0.0005832603437575339</v>
       </c>
       <c r="J5" t="n">
-        <v>2.221023784335904e-05</v>
+        <v>2.221023784335882e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05108145198441414</v>
+        <v>0.05108145198441404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000234481341296611</v>
+        <v>0.0002344813412966112</v>
       </c>
       <c r="M5" t="n">
         <v>1.432599990435134</v>
@@ -688,34 +688,34 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.612449863941507</v>
+        <v>2.612449863941506</v>
       </c>
       <c r="E6" t="n">
         <v>0.165448788679351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9685272857894484</v>
+        <v>0.9685272857894489</v>
       </c>
       <c r="G6" t="n">
         <v>0.008803216561351725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005755797827749523</v>
+        <v>0.005755797827749522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002593664518785657</v>
+        <v>0.0002593664518785399</v>
       </c>
       <c r="J6" t="n">
-        <v>1.970247582360286e-05</v>
+        <v>1.970247582360283e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03080138859357326</v>
+        <v>0.0308013885935732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002343257814860045</v>
+        <v>0.0002343257814860046</v>
       </c>
       <c r="M6" t="n">
-        <v>1.432599991780845</v>
+        <v>1.432599991780844</v>
       </c>
     </row>
     <row r="7">
@@ -739,25 +739,25 @@
         <v>0.1615019614938295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9625373585235353</v>
+        <v>0.9625373585235348</v>
       </c>
       <c r="G7" t="n">
         <v>0.002664909953161935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005183495819838593</v>
+        <v>0.0051834958198386</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001351527580921877</v>
+        <v>0.0001351527580920906</v>
       </c>
       <c r="J7" t="n">
-        <v>1.837741014355906e-05</v>
+        <v>1.837741014355898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02525078206769121</v>
+        <v>0.02525078206769123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002339038671066824</v>
+        <v>0.0002339038671066825</v>
       </c>
       <c r="M7" t="n">
         <v>1.43259999228663</v>
@@ -784,25 +784,25 @@
         <v>0.1600401217258293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9594933224300903</v>
+        <v>0.9594933224300901</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00100873894466173</v>
+        <v>0.001008738944661736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004997759118034201</v>
+        <v>0.004997759118034206</v>
       </c>
       <c r="I8" t="n">
-        <v>5.141759203917151e-05</v>
+        <v>5.141759203956029e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.784742985847446e-05</v>
+        <v>1.784742985847452e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02343665449195835</v>
+        <v>0.02343665449195834</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002337225489288063</v>
+        <v>0.0002337225489288062</v>
       </c>
       <c r="M8" t="n">
         <v>1.432599992475247</v>
@@ -829,25 +829,25 @@
         <v>0.1724597851737661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9820751158796159</v>
+        <v>0.9820751158796165</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02602822705092953</v>
+        <v>0.02602822705092948</v>
       </c>
       <c r="H9" t="n">
         <v>0.006535004021761003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005231448288668785</v>
+        <v>0.0005231448288665187</v>
       </c>
       <c r="J9" t="n">
-        <v>2.211240974831632e-05</v>
+        <v>2.211240974831636e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04646075348385699</v>
+        <v>0.04646075348385697</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002346341295683079</v>
+        <v>0.000234634129568308</v>
       </c>
       <c r="M9" t="n">
         <v>1.432599990576075</v>
@@ -874,22 +874,22 @@
         <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9727659338281381</v>
+        <v>0.972765933828138</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01112061915572762</v>
+        <v>0.01112061915572759</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005847858327735188</v>
+        <v>0.005847858327735198</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003082891040218845</v>
+        <v>0.0003082891040223327</v>
       </c>
       <c r="J10" t="n">
-        <v>2.015830940726062e-05</v>
+        <v>2.015830940726065e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03596719112729574</v>
+        <v>0.03596719112729573</v>
       </c>
       <c r="L10" t="n">
         <v>0.0002342417742032933</v>
@@ -919,25 +919,25 @@
         <v>0.1627298041679663</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9646725810266092</v>
+        <v>0.9646725810266091</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001916112446268599</v>
+        <v>0.001916112446268605</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005419358970709854</v>
+        <v>0.005419358970709861</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001967717792873163</v>
+        <v>0.0001967717792880828</v>
       </c>
       <c r="J11" t="n">
-        <v>1.895508401788367e-05</v>
+        <v>1.895508401788379e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02772923758671252</v>
+        <v>0.02772923758671257</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002340507071139726</v>
+        <v>0.0002340507071139727</v>
       </c>
       <c r="M11" t="n">
         <v>1.432599992189783</v>
@@ -954,7 +954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1015,6 +1015,11 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>carbon dioxide storage from natural gas, post, 200km pipeline, storage 1000m</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>direct emissions</t>
         </is>
       </c>
@@ -1034,7 +1039,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.968528699246639</v>
+        <v>0.8318795385908728</v>
       </c>
       <c r="E2" t="n">
         <v>0.1770046506426656</v>
@@ -1043,25 +1048,28 @@
         <v>0.4050818133788934</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03332028509091799</v>
+        <v>0.033320285090918</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007134522571586236</v>
+        <v>0.007134522571586243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007426560757673144</v>
+        <v>0.0007426560757672062</v>
       </c>
       <c r="J2" t="n">
-        <v>2.366558390921168e-05</v>
+        <v>2.366558390921172e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05605377579863238</v>
+        <v>0.05605377579863243</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349047987132504</v>
+        <v>0.0002349047987132502</v>
       </c>
       <c r="M2" t="n">
-        <v>1.288932425305554</v>
+        <v>0.008583278267245137</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1436999863825423</v>
       </c>
     </row>
     <row r="3">
@@ -1079,34 +1087,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.952221978677433</v>
+        <v>0.8152480453597405</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1753652466821184</v>
+        <v>0.1753652466821185</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3962681169435137</v>
+        <v>0.3962681169435139</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03207727081048767</v>
+        <v>0.03207727081048773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006950845406861199</v>
+        <v>0.006950845406861223</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006728322794243694</v>
+        <v>0.0006728322794234023</v>
       </c>
       <c r="J3" t="n">
-        <v>2.292703187514291e-05</v>
+        <v>2.292703187514303e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05169753441829467</v>
+        <v>0.05169753441829482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002347794527370768</v>
+        <v>0.0002347794527370767</v>
       </c>
       <c r="M3" t="n">
-        <v>1.288932425652121</v>
+        <v>0.008258505609787437</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1436999867246413</v>
       </c>
     </row>
     <row r="4">
@@ -1124,34 +1135,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.937127987001214</v>
+        <v>0.7997184875429971</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1742297025430327</v>
+        <v>0.1742297025430324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3852239220152076</v>
+        <v>0.3852239220152072</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03041962716113818</v>
+        <v>0.03041962716113816</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006725871138007352</v>
+        <v>0.006725871138007343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00064320793683306</v>
+        <v>0.0006432079368323447</v>
       </c>
       <c r="J4" t="n">
-        <v>2.238978961716152e-05</v>
+        <v>2.23897896171615e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05069627631781804</v>
+        <v>0.05069627631781801</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002345640871387255</v>
+        <v>0.0002345640871387254</v>
       </c>
       <c r="M4" t="n">
-        <v>1.288932426012422</v>
+        <v>0.007822939475260528</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1436999870789452</v>
       </c>
     </row>
     <row r="5">
@@ -1169,34 +1183,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.916356514038502</v>
+        <v>0.7782462901972031</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909712</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3677393594387464</v>
+        <v>0.3677393594387462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02768872593440493</v>
+        <v>0.02768872593440492</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006597103534782493</v>
+        <v>0.006597103534782496</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005832603437571993</v>
+        <v>0.0005832603437575339</v>
       </c>
       <c r="J5" t="n">
-        <v>2.221023784335904e-05</v>
+        <v>2.221023784335882e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05108145198441414</v>
+        <v>0.05108145198441404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000234481341296611</v>
+        <v>0.0002344813412966112</v>
       </c>
       <c r="M5" t="n">
-        <v>1.288932426532286</v>
+        <v>0.007122215101819614</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1436999875891669</v>
       </c>
     </row>
     <row r="6">
@@ -1214,34 +1231,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.746729894688288</v>
+        <v>0.603800999076991</v>
       </c>
       <c r="E6" t="n">
         <v>0.165448788679351</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2464748778604278</v>
+        <v>0.2464748778604279</v>
       </c>
       <c r="G6" t="n">
         <v>0.008803216561351725</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005755797827749523</v>
+        <v>0.005755797827749522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002593664518785657</v>
+        <v>0.0002593664518785399</v>
       </c>
       <c r="J6" t="n">
-        <v>1.970247582360286e-05</v>
+        <v>1.970247582360283e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03080138859357326</v>
+        <v>0.0308013885935732</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002343257814860045</v>
+        <v>0.0002343257814860046</v>
       </c>
       <c r="M6" t="n">
-        <v>1.288932430456647</v>
+        <v>0.002303543398138431</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1436999914472111</v>
       </c>
     </row>
     <row r="7">
@@ -1259,34 +1279,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.690153426011455</v>
+        <v>0.5456271042085689</v>
       </c>
       <c r="E7" t="n">
         <v>0.1615019614938295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.206232410855022</v>
+        <v>0.2062324108550221</v>
       </c>
       <c r="G7" t="n">
         <v>0.002664909953161935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005183495819838593</v>
+        <v>0.0051834958198386</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001351527580921877</v>
+        <v>0.0001351527580920906</v>
       </c>
       <c r="J7" t="n">
-        <v>1.837741014355906e-05</v>
+        <v>1.837741014355898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02525078206769121</v>
+        <v>0.02525078206769123</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002339038671066824</v>
+        <v>0.0002339038671066825</v>
       </c>
       <c r="M7" t="n">
-        <v>1.28893243178657</v>
+        <v>0.0007061172285335846</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1436999927551496</v>
       </c>
     </row>
     <row r="8">
@@ -1304,34 +1327,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.673886330969188</v>
+        <v>0.5289141390947195</v>
       </c>
       <c r="E8" t="n">
         <v>0.1600401217258293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1951676369497101</v>
+        <v>0.1951676369497102</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00100873894466173</v>
+        <v>0.001008738944661736</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004997759118034201</v>
+        <v>0.004997759118034206</v>
       </c>
       <c r="I8" t="n">
-        <v>5.141759203917151e-05</v>
+        <v>5.141759203956029e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.784742985847446e-05</v>
+        <v>1.784742985847452e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02343665449195835</v>
+        <v>0.02343665449195834</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002337225489288063</v>
+        <v>0.0002337225489288062</v>
       </c>
       <c r="M8" t="n">
-        <v>1.288932432168167</v>
+        <v>0.0002602471630873567</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.1436999931306115</v>
       </c>
     </row>
     <row r="9">
@@ -1349,34 +1375,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.897980047276503</v>
+        <v>0.7594535033520344</v>
       </c>
       <c r="E9" t="n">
         <v>0.1724597851737661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3567839592542623</v>
+        <v>0.3567839592542621</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02602822705092953</v>
+        <v>0.02602822705092948</v>
       </c>
       <c r="H9" t="n">
         <v>0.006535004021761003</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005231448288668785</v>
+        <v>0.0005231448288665187</v>
       </c>
       <c r="J9" t="n">
-        <v>2.211240974831632e-05</v>
+        <v>2.211240974831636e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04646075348385699</v>
+        <v>0.04646075348385697</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002346341295683079</v>
+        <v>0.000234634129568308</v>
       </c>
       <c r="M9" t="n">
-        <v>1.288932426923744</v>
+        <v>0.006705895024379863</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1436999879748957</v>
       </c>
     </row>
     <row r="10">
@@ -1394,34 +1423,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.770432118235289</v>
+        <v>0.6280942224721918</v>
       </c>
       <c r="E10" t="n">
         <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2613919696581965</v>
+        <v>0.2613919696581963</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01112061915572762</v>
+        <v>0.01112061915572759</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005847858327735188</v>
+        <v>0.005847858327735198</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003082891040218845</v>
+        <v>0.0003082891040223327</v>
       </c>
       <c r="J10" t="n">
-        <v>2.015830940726062e-05</v>
+        <v>2.015830940726065e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03596719112729574</v>
+        <v>0.03596719112729573</v>
       </c>
       <c r="L10" t="n">
         <v>0.0002342417742032933</v>
       </c>
       <c r="M10" t="n">
-        <v>1.288932429941687</v>
+        <v>0.00289454323820552</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.143699990940384</v>
       </c>
     </row>
     <row r="11">
@@ -1439,34 +1471,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.68970516356903</v>
+        <v>0.5450259545139013</v>
       </c>
       <c r="E11" t="n">
         <v>0.1627298041679663</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2025284409967362</v>
+        <v>0.2025284409967361</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001916112446268599</v>
+        <v>0.001916112446268605</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005419358970709854</v>
+        <v>0.005419358970709861</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001967717792873163</v>
+        <v>0.0001967717792880828</v>
       </c>
       <c r="J11" t="n">
-        <v>1.895508401788367e-05</v>
+        <v>1.895508401788379e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02772923758671252</v>
+        <v>0.02772923758671257</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002340507071139726</v>
+        <v>0.0002340507071139727</v>
       </c>
       <c r="M11" t="n">
-        <v>1.288932431830218</v>
+        <v>0.0005532299783946957</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1436999927966933</v>
       </c>
     </row>
   </sheetData>
@@ -1550,28 +1585,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8537556471123281</v>
+        <v>0.8537556471123287</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003092361873368597</v>
+        <v>0.0003092361873368602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001274586581092431</v>
+        <v>0.0001274586581092432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04634287500342411</v>
+        <v>0.04634287500342419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3763015622064995</v>
+        <v>0.3763015622064996</v>
       </c>
       <c r="I2" t="n">
         <v>2.87180036450661e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4222372346777837</v>
+        <v>0.4222372346777835</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436993199138265</v>
+        <v>0.00843699319913882</v>
       </c>
     </row>
     <row r="3">
@@ -1589,28 +1624,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7925894383766168</v>
+        <v>0.7925894383766189</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002878884378641578</v>
+        <v>0.0002878884378641586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001211983546970557</v>
+        <v>0.0001211983546970561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04274132012335732</v>
+        <v>0.04274132012335749</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3622636206254295</v>
+        <v>0.3622636206254305</v>
       </c>
       <c r="I3" t="n">
-        <v>2.658305254751579e-07</v>
+        <v>2.658305254751578e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3787381513588891</v>
+        <v>0.3787381513588897</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436993645854152</v>
+        <v>0.008436993645854485</v>
       </c>
     </row>
     <row r="4">
@@ -1628,28 +1663,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7358395778613145</v>
+        <v>0.7358395778613146</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045913</v>
+        <v>0.0002813057792045906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001165917847242303</v>
+        <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047336</v>
+        <v>0.04191352256047332</v>
       </c>
       <c r="H4" t="n">
-        <v>0.343543075674212</v>
+        <v>0.3435430756742119</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425216e-07</v>
+        <v>2.28692724242526e-07</v>
       </c>
       <c r="J4" t="n">
         <v>0.3415478593147128</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436994055263325</v>
+        <v>0.008436994055263547</v>
       </c>
     </row>
     <row r="5">
@@ -1667,28 +1702,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.69764693455947</v>
+        <v>0.697646934559469</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002755396677122543</v>
+        <v>0.0002755396677122545</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001094272460916249</v>
+        <v>0.0001094272460916247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044274</v>
+        <v>0.04223196940044265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784111</v>
+        <v>0.312701730978411</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810023e-07</v>
+        <v>2.075700053810011e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.33389106528868</v>
+        <v>0.3338910652886785</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436994408126841</v>
+        <v>0.008436994408127618</v>
       </c>
     </row>
     <row r="6">
@@ -1706,28 +1741,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4042680512618932</v>
+        <v>0.4042680512618922</v>
       </c>
       <c r="E6" t="n">
         <v>0.0001615158763762971</v>
       </c>
       <c r="F6" t="n">
-        <v>4.955266986951886e-05</v>
+        <v>4.955266986951885e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.02546527653465741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0994188415687266</v>
+        <v>0.09941884156872666</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67630390188655e-07</v>
+        <v>1.676303901886784e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2707356997273885</v>
+        <v>0.2707356997273899</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436997254484657</v>
+        <v>0.008436997254482215</v>
       </c>
     </row>
     <row r="7">
@@ -1745,28 +1780,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2769355120041206</v>
+        <v>0.2769355120041218</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
-        <v>3.12911805157343e-05</v>
+        <v>3.129118051573436e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02087627140953937</v>
+        <v>0.0208762714095394</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03009607438166323</v>
+        <v>0.03009607438166318</v>
       </c>
       <c r="I7" t="n">
-        <v>7.979581528031507e-08</v>
+        <v>7.979581528031407e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2173620713574961</v>
+        <v>0.2173620713574963</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998341688151</v>
+        <v>0.008436998341689095</v>
       </c>
     </row>
     <row r="8">
@@ -1784,28 +1819,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2424674618526513</v>
+        <v>0.2424674618526505</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001216429948959389</v>
+        <v>0.000121642994895939</v>
       </c>
       <c r="F8" t="n">
-        <v>2.540593178078801e-05</v>
+        <v>2.540593178078809e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01937642797732396</v>
+        <v>0.01937642797732395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139216065225714</v>
+        <v>0.0113921606522572</v>
       </c>
       <c r="I8" t="n">
-        <v>3.444042669698768e-08</v>
+        <v>3.444042669698805e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2031147912169418</v>
+        <v>0.2031147912169408</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998639025028</v>
+        <v>0.008436998639025084</v>
       </c>
     </row>
     <row r="9">
@@ -1823,28 +1858,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.6857950294355106</v>
+        <v>0.6857950294355112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002582399815828589</v>
+        <v>0.0002582399815828585</v>
       </c>
       <c r="F9" t="n">
         <v>0.0001037243484913611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03841177263423207</v>
+        <v>0.03841177263423204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2939489405329222</v>
+        <v>0.2939489405329215</v>
       </c>
       <c r="I9" t="n">
-        <v>2.352387166130046e-07</v>
+        <v>2.352387166130071e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3446351220860778</v>
+        <v>0.3446351220860779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436994613487681</v>
+        <v>0.008436994613488902</v>
       </c>
     </row>
     <row r="10">
@@ -1862,28 +1897,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.431730817717637</v>
+        <v>0.4317308177176368</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002006880166748547</v>
+        <v>0.0002006880166748548</v>
       </c>
       <c r="F10" t="n">
-        <v>6.324602195601301e-05</v>
+        <v>6.324602195601296e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02973614210440395</v>
+        <v>0.02973614210440396</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1255903528311782</v>
+        <v>0.1255903528311779</v>
       </c>
       <c r="I10" t="n">
-        <v>1.567269304237358e-07</v>
+        <v>1.567269304237354e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2677032350937341</v>
+        <v>0.2677032350937339</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00843699692275951</v>
+        <v>0.008436996922759676</v>
       </c>
     </row>
     <row r="11">
@@ -1901,28 +1936,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2858980513713267</v>
+        <v>0.2858980513713275</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001403214666166645</v>
+        <v>0.0001403214666166643</v>
       </c>
       <c r="F11" t="n">
-        <v>3.125804518334548e-05</v>
+        <v>3.125804518334551e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02292535289750496</v>
+        <v>0.02292535289750498</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02163955395119727</v>
+        <v>0.02163955395119724</v>
       </c>
       <c r="I11" t="n">
         <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2327244551954743</v>
+        <v>0.2327244551954737</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436998307552734</v>
+        <v>0.008436998307554067</v>
       </c>
     </row>
   </sheetData>
@@ -2009,25 +2044,25 @@
         <v>1.146704692771251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003092361873368597</v>
+        <v>0.0003092361873368602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001274586581092431</v>
+        <v>0.0001274586581092432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04634287500342411</v>
+        <v>0.04634287500342419</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3763015622064995</v>
+        <v>0.3763015622064996</v>
       </c>
       <c r="I2" t="n">
         <v>2.87180036450661e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7151862819240815</v>
+        <v>0.7151862819240824</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436991611763034</v>
+        <v>0.00843699161176259</v>
       </c>
     </row>
     <row r="3">
@@ -2045,28 +2080,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.005200607422688</v>
+        <v>1.005200607422689</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002878884378641578</v>
+        <v>0.0002878884378641586</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001211983546970557</v>
+        <v>0.0001211983546970561</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04274132012335732</v>
+        <v>0.04274132012335749</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3622636206254295</v>
+        <v>0.3622636206254305</v>
       </c>
       <c r="I3" t="n">
-        <v>2.658305254751579e-07</v>
+        <v>2.658305254751578e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5913493215570135</v>
+        <v>0.591349321557015</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436992493800588</v>
+        <v>0.008436992493799145</v>
       </c>
     </row>
     <row r="4">
@@ -2084,28 +2119,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9083785276337037</v>
+        <v>0.908378527633703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045913</v>
+        <v>0.0002813057792045906</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0001165917847242303</v>
+        <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047336</v>
+        <v>0.04191352256047332</v>
       </c>
       <c r="H4" t="n">
-        <v>0.343543075674212</v>
+        <v>0.3435430756742119</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425216e-07</v>
+        <v>2.28692724242526e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5140868100220193</v>
+        <v>0.5140868100220204</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00843699312034607</v>
+        <v>0.008436993120344294</v>
       </c>
     </row>
     <row r="5">
@@ -2123,28 +2158,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8457793535109432</v>
+        <v>0.8457793535109419</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002755396677122543</v>
+        <v>0.0002755396677122545</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0001094272460916249</v>
+        <v>0.0001094272460916247</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044274</v>
+        <v>0.04223196940044265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784111</v>
+        <v>0.312701730978411</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810023e-07</v>
+        <v>2.075700053810011e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4820234850428222</v>
+        <v>0.4820234850428235</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436993605457799</v>
+        <v>0.008436993605455467</v>
       </c>
     </row>
     <row r="6">
@@ -2162,28 +2197,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.537468974566251</v>
+        <v>0.5374689745662496</v>
       </c>
       <c r="E6" t="n">
         <v>0.0001615158763762971</v>
       </c>
       <c r="F6" t="n">
-        <v>4.955266986951886e-05</v>
+        <v>4.955266986951885e-05</v>
       </c>
       <c r="G6" t="n">
         <v>0.02546527653465741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0994188415687266</v>
+        <v>0.09941884156872666</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67630390188655e-07</v>
+        <v>1.676303901886784e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.403936623753513</v>
+        <v>0.4039366237535111</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436996532718011</v>
+        <v>0.008436996532718566</v>
       </c>
     </row>
     <row r="7">
@@ -2201,28 +2236,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3826245304114747</v>
+        <v>0.3826245304114752</v>
       </c>
       <c r="E7" t="n">
         <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
-        <v>3.12911805157343e-05</v>
+        <v>3.129118051573436e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02087627140953937</v>
+        <v>0.0208762714095394</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03009607438166323</v>
+        <v>0.03009607438166318</v>
       </c>
       <c r="I7" t="n">
-        <v>7.979581528031507e-08</v>
+        <v>7.979581528031407e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3230510903375374</v>
+        <v>0.3230510903375379</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436997769000865</v>
+        <v>0.00843699776900092</v>
       </c>
     </row>
     <row r="8">
@@ -2240,28 +2275,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3345958313526998</v>
+        <v>0.3345958313526991</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001216429948959389</v>
+        <v>0.000121642994895939</v>
       </c>
       <c r="F8" t="n">
-        <v>2.540593178078801e-05</v>
+        <v>2.540593178078809e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01937642797732396</v>
+        <v>0.01937642797732395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139216065225714</v>
+        <v>0.0113921606522572</v>
       </c>
       <c r="I8" t="n">
-        <v>3.444042669698768e-08</v>
+        <v>3.444042669698805e-08</v>
       </c>
       <c r="J8" t="n">
         <v>0.2952431612161974</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998139817908</v>
+        <v>0.008436998139817131</v>
       </c>
     </row>
     <row r="9">
@@ -2279,28 +2314,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8897190975905908</v>
+        <v>0.8897190975905903</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002582399815828589</v>
+        <v>0.0002582399815828585</v>
       </c>
       <c r="F9" t="n">
         <v>0.0001037243484913611</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03841177263423207</v>
+        <v>0.03841177263423204</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2939489405329222</v>
+        <v>0.2939489405329215</v>
       </c>
       <c r="I9" t="n">
-        <v>2.352387166130046e-07</v>
+        <v>2.352387166130071e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5485591913461401</v>
+        <v>0.5485591913461402</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436993508505575</v>
+        <v>0.008436993508505686</v>
       </c>
     </row>
     <row r="10">
@@ -2318,28 +2353,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5828353310743951</v>
+        <v>0.5828353310743956</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0002006880166748547</v>
+        <v>0.0002006880166748548</v>
       </c>
       <c r="F10" t="n">
-        <v>6.324602195601301e-05</v>
+        <v>6.324602195601296e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02973614210440395</v>
+        <v>0.02973614210440396</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1255903528311782</v>
+        <v>0.1255903528311779</v>
       </c>
       <c r="I10" t="n">
-        <v>1.567269304237358e-07</v>
+        <v>1.567269304237354e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4188077492692678</v>
+        <v>0.4188077492692682</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436996103983851</v>
+        <v>0.008436996103984185</v>
       </c>
     </row>
     <row r="11">
@@ -2357,28 +2392,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3788320991683782</v>
+        <v>0.378832099168378</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001403214666166645</v>
+        <v>0.0001403214666166643</v>
       </c>
       <c r="F11" t="n">
-        <v>3.125804518334548e-05</v>
+        <v>3.125804518334551e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02292535289750496</v>
+        <v>0.02292535289750498</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02163955395119727</v>
+        <v>0.02163955395119724</v>
       </c>
       <c r="I11" t="n">
         <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3256585034960959</v>
+        <v>0.3256585034960964</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00843699780398266</v>
+        <v>0.008436997803981883</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\Phase 2\Ammonia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D10C80-288A-4E48-A78E-01F203747E70}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9827796-91DE-4CA2-8E73-9208716C3CB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ammoniaBAU" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
@@ -947,422 +947,6 @@
         <v>1.432599992189783</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>6.5611814722822475</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:M14" si="0">F2/$D2*100</f>
-        <v>36.720941156848539</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>1.2351112606133796</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>0.26446139771079968</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.752866247813212E-2</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>8.7723226543536459E-4</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>2.0777928370024412</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>8.7074153558768727E-3</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>53.103398565443136</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>0.38786368989503472</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:M15" si="1">E3/$D3*100</f>
-        <v>6.5257232064034945</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>36.753380770082046</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>1.1936651901475854</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>0.25865611364775953</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>2.5037556202966674E-2</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>8.5316484760962258E-4</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>1.9237779802451012</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>8.7366553641627463E-3</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>53.310169363059266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>0.6179553282417064</v>
-      </c>
-      <c r="E16">
-        <f t="shared" ref="E16:M16" si="2">E4/$D4*100</f>
-        <v>6.4984778079905618</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="2"/>
-        <v>36.758001399030114</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="2"/>
-        <v>1.134601443661299</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="2"/>
-        <v>0.25086379470199505</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="2"/>
-        <v>2.399058508635182E-2</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="2"/>
-        <v>8.3510187315371815E-4</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="2"/>
-        <v>1.8908866960714028</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="2"/>
-        <v>8.7488498951324746E-3</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="2"/>
-        <v>53.433594321690016</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>0.84709771968081526</v>
-      </c>
-      <c r="E17">
-        <f t="shared" ref="E17:M17" si="3">E5/$D5*100</f>
-        <v>6.4853748543562624</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="3"/>
-        <v>36.734728736203266</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="3"/>
-        <v>1.0351300452201979</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="3"/>
-        <v>0.24662962450708004</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="3"/>
-        <v>2.1804914658737979E-2</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="3"/>
-        <v>8.3031933493842339E-4</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="3"/>
-        <v>1.9096561476972227</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="3"/>
-        <v>8.7659750757278863E-3</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="3"/>
-        <v>53.557079382946569</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>3.1621057281551472</v>
-      </c>
-      <c r="E18">
-        <f t="shared" ref="E18:M18" si="4">E6/$D6*100</f>
-        <v>6.3330895250074546</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="4"/>
-        <v>37.073526239014349</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="4"/>
-        <v>0.33697169399721855</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="4"/>
-        <v>0.22032184836135085</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="4"/>
-        <v>9.9280929926526332E-3</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="4"/>
-        <v>7.5417622728563786E-4</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="4"/>
-        <v>1.1790231467677597</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="4"/>
-        <v>8.96958003750809E-3</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="4"/>
-        <v>54.837415697594437</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>3.9896057616725087</v>
-      </c>
-      <c r="E19">
-        <f t="shared" ref="E19:M19" si="5">E7/$D7*100</f>
-        <v>6.2352937887152233</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="5"/>
-        <v>37.161797649358348</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="5"/>
-        <v>0.1028872734717272</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="5"/>
-        <v>0.20012524300211565</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="5"/>
-        <v>5.2179994921705102E-3</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="5"/>
-        <v>7.095180161337145E-4</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="5"/>
-        <v>0.97488626844258119</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="5"/>
-        <v>9.0305982431209773E-3</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="5"/>
-        <v>55.310051661258562</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>4.2952804845888677</v>
-      </c>
-      <c r="E20">
-        <f t="shared" ref="E20:M20" si="6">E8/$D8*100</f>
-        <v>6.1985897083113137</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="6"/>
-        <v>37.162590039749404</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="6"/>
-        <v>3.9069945544435956E-2</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="6"/>
-        <v>0.19357057405103226</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="6"/>
-        <v>1.9914790954019229E-3</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="6"/>
-        <v>6.9125725379083809E-4</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="6"/>
-        <v>0.90773615868635582</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="6"/>
-        <v>9.0524186733142685E-3</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="6"/>
-        <v>55.486708418634933</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>1.1423193353657324</v>
-      </c>
-      <c r="E21">
-        <f t="shared" ref="E21:M21" si="7">E9/$D9*100</f>
-        <v>6.4665821079921733</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="7"/>
-        <v>36.824059398268965</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="7"/>
-        <v>0.9759589296757496</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="7"/>
-        <v>0.24503764770550632</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="7"/>
-        <v>1.9615929515557927E-2</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="7"/>
-        <v>8.2913076285569688E-4</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="7"/>
-        <v>1.7421004954855217</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="7"/>
-        <v>8.7978821419843721E-3</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="7"/>
-        <v>53.717018478451692</v>
-      </c>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>2.6793422300261445</v>
-      </c>
-      <c r="E22">
-        <f t="shared" ref="E22:M22" si="8">E10/$D10*100</f>
-        <v>6.3458782463359729</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="8"/>
-        <v>37.051064521491455</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="8"/>
-        <v>0.42356620799448325</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="8"/>
-        <v>0.22273536590739382</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="8"/>
-        <v>1.1742228101526303E-2</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="8"/>
-        <v>7.6779705838728271E-4</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="8"/>
-        <v>1.3699315249146959</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="8"/>
-        <v>8.921886332388964E-3</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="8"/>
-        <v>54.565392221863696</v>
-      </c>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>3.7897755964635564</v>
-      </c>
-      <c r="E23">
-        <f t="shared" ref="E23:M23" si="9">E11/$D11*100</f>
-        <v>6.2696492720831012</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="9"/>
-        <v>37.166877796947531</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="9"/>
-        <v>7.3823925896066331E-2</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="9"/>
-        <v>0.20879690846796117</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="9"/>
-        <v>7.5812175224314535E-3</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="9"/>
-        <v>7.3030093855660995E-4</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="9"/>
-        <v>1.0683512779964071</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="9"/>
-        <v>9.0174989946710579E-3</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="9"/>
-        <v>55.195171801153286</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1370,7 +954,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1852,422 +1436,6 @@
       </c>
       <c r="N11">
         <v>0.14369999279669329</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>21.277678129034783</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:M14" si="0">F2/$D2*100</f>
-        <v>48.694768243135847</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>4.0054218844424865</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>0.85763890570880796</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>8.9274473203800275E-2</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>2.8448330330733988E-3</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>6.7382082619296488</v>
-      </c>
-      <c r="L14">
-        <f t="shared" si="0"/>
-        <v>2.8237838270569467E-2</v>
-      </c>
-      <c r="M14">
-        <f t="shared" si="0"/>
-        <v>1.0317934110730045</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>1.9992670163885204</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:M23" si="1">E3/$D3*100</f>
-        <v>21.510661409158725</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>48.607061274051212</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>3.934663933641589</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>0.85260497666008606</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>8.2530989586918291E-2</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>2.8122768285848672E-3</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>6.3413257734929616</v>
-      </c>
-      <c r="L15">
-        <f t="shared" si="1"/>
-        <v>2.8798529977888718E-2</v>
-      </c>
-      <c r="M15">
-        <f t="shared" si="1"/>
-        <v>1.0130052634647222</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>3.866070693643163</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>21.786379239315121</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>48.169940799886227</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>3.8037919136516947</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>0.84102984272271497</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>8.0429294414400096E-2</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>2.7997088933069971E-3</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>6.3392652674035261</v>
-      </c>
-      <c r="L16">
-        <f t="shared" si="1"/>
-        <v>2.9330832135616221E-2</v>
-      </c>
-      <c r="M16">
-        <f t="shared" si="1"/>
-        <v>0.97821165786665965</v>
-      </c>
-    </row>
-    <row r="17" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>6.4472373589714032</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>22.290821925667398</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>47.252311263258726</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>3.5578359040283702</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>0.84768840120147926</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>7.4945470489777608E-2</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>2.8538829061081515E-3</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>6.563661481954548</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="1"/>
-        <v>3.0129451852214419E-2</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="1"/>
-        <v>0.91516210119226971</v>
-      </c>
-    </row>
-    <row r="18" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>27.417255616146758</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>27.40121148064787</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>40.820548200020404</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>1.4579665444093148</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>0.95326073268315292</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>4.2955618204511777E-2</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>3.2630743993006476E-3</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>5.1012483650504352</v>
-      </c>
-      <c r="L18">
-        <f t="shared" si="1"/>
-        <v>3.8808445471970071E-2</v>
-      </c>
-      <c r="M18">
-        <f t="shared" si="1"/>
-        <v>0.38150705309527072</v>
-      </c>
-    </row>
-    <row r="19" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>34.4103227814918</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>29.599328964437682</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>37.797317850285658</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.48841231174308719</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>0.95000702491809896</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.4770169416002425E-2</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>3.3681263269014802E-3</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>4.6278459909570371</v>
-      </c>
-      <c r="L19">
-        <f t="shared" si="1"/>
-        <v>4.2868813756230022E-2</v>
-      </c>
-      <c r="M19">
-        <f t="shared" si="1"/>
-        <v>0.12941388415038624</v>
-      </c>
-    </row>
-    <row r="20" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>36.419383509462051</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>30.258242292359828</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>36.899682296970887</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>0.19071884642529624</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>0.94490934324204034</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>9.7213495043951305E-3</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>3.374352950560535E-3</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>4.431088670095324</v>
-      </c>
-      <c r="L20">
-        <f t="shared" si="1"/>
-        <v>4.4189128566092369E-2</v>
-      </c>
-      <c r="M20">
-        <f t="shared" si="1"/>
-        <v>4.9204047283135849E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>8.7063128588931775</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>22.708406033097813</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>46.979039227485096</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>3.4272311518805969</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>0.86048770502962446</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>6.8884378906343927E-2</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>2.9116212711795797E-3</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>6.1176560880674105</v>
-      </c>
-      <c r="L21">
-        <f t="shared" si="1"/>
-        <v>3.0895127684933004E-2</v>
-      </c>
-      <c r="M21">
-        <f t="shared" si="1"/>
-        <v>0.88298954376821603</v>
-      </c>
-    </row>
-    <row r="22" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>24.496974221036201</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>26.526173124350155</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>41.616681113440606</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>1.7705335852249371</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>0.93104794129739121</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>4.9083257414612155E-2</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>3.2094403492388653E-3</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>5.7264005686484625</v>
-      </c>
-      <c r="L22">
-        <f t="shared" si="1"/>
-        <v>3.729405013173228E-2</v>
-      </c>
-      <c r="M22">
-        <f t="shared" si="1"/>
-        <v>0.46084538507813971</v>
-      </c>
-    </row>
-    <row r="23" spans="4:13" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>34.482586813335374</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>29.857257772815981</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>37.159412193015193</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.3515635228743465</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>0.99433043983075764</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>3.6103194289816891E-2</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>3.4778314428694471E-3</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>5.0876912112275043</v>
-      </c>
-      <c r="L23">
-        <f t="shared" si="1"/>
-        <v>4.2943038799449149E-2</v>
-      </c>
-      <c r="M23">
-        <f t="shared" si="1"/>
-        <v>0.10150525379807121</v>
       </c>
     </row>
   </sheetData>
@@ -2277,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -2660,342 +1828,6 @@
       </c>
       <c r="K11">
         <v>8.4369983075540667E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>3.6220690121675295E-2</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:M14" si="0">F2/$D2*100</f>
-        <v>1.4929173064957011E-2</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>5.4281192938717808</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>44.07602614158634</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>3.3637263474858952E-5</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>49.456449993147714</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0.98822107094405731</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>7.164369447229217</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:M23" si="1">E3/$D3*100</f>
-        <v>3.6322517551307713E-2</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>1.5291442054198259E-2</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>5.3926179247228214</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>45.706339636245794</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>3.3539498838090964E-5</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>47.784910196964134</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>1.0644847429629052</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>13.811454091090756</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>3.8229226541767906E-2</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>1.5844728692509188E-2</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>5.6960136178449572</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>46.687224499761854</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>3.1079155174992266E-5</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>46.416076219684548</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>1.1465806283191915</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>18.284940554228672</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>3.9495574919460479E-2</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>1.5685189839001131E-2</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>6.0534874172578625</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>44.822347162733152</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>2.9752872849942601E-5</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>47.859604729649519</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>1.2093501727281553</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>52.64827206364555</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>3.9952668995765925E-2</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>1.2257379655613134E-2</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>6.2991068562478461</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>24.592307321441368</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>4.1465158986823913E-5</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>66.96935334917238</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>2.0869809593280411</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>67.562672886462863</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>4.7926514170121295E-2</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>1.1299085584686097E-2</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>7.5383150605938489</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>10.867538859088336</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.8813861647012756E-5</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>78.488334625088157</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>3.0465570416131831</v>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>71.599899494339851</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>5.0168791295329543E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>1.0478078826192146E-2</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>7.9913518413036249</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>4.6984286325314493</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.4204143695749901E-5</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>83.769916864298821</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>3.4796415876008622</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>19.673148663193427</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>3.7655563324134902E-2</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>1.5124686537424785E-2</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>5.6010573109358024</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>42.86250671354027</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>3.4301607115268217E-5</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>50.253371239764242</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>1.2302501842910012</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>49.431571061592763</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>4.648452425421018E-2</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>1.4649411012715221E-2</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>6.887657976700698</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>29.089967099202369</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>3.6302002079045207E-5</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>62.006978447579527</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>1.9542262392483856</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>66.512894838432388</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>4.908094544317592E-2</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>1.0933283746921107E-2</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>8.0187160379520321</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>7.56897567066365</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>3.9002643381364024E-5</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>81.401203708523568</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>2.9510513510272238</v>
       </c>
     </row>
   </sheetData>
@@ -3005,7 +1837,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -3390,342 +2222,6 @@
         <v>8.4369978039818827E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f>E2/$D2*100</f>
-        <v>2.6967377851182108E-2</v>
-      </c>
-      <c r="F14">
-        <f t="shared" ref="F14:M14" si="0">F2/$D2*100</f>
-        <v>1.1115212043059909E-2</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="0"/>
-        <v>4.0413957748290859</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>32.815908453037579</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="0"/>
-        <v>2.5043940106029442E-5</v>
-      </c>
-      <c r="J14">
-        <f t="shared" si="0"/>
-        <v>62.368828385596444</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="0"/>
-        <v>0.73575975270257599</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D15">
-        <f>($D$2-D3)/$D$2*100</f>
-        <v>12.340063334579014</v>
-      </c>
-      <c r="E15">
-        <f t="shared" ref="E15:M23" si="1">E3/$D3*100</f>
-        <v>2.863989891553069E-2</v>
-      </c>
-      <c r="F15">
-        <f t="shared" si="1"/>
-        <v>1.2057131064395781E-2</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>4.2520189311211469</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="1"/>
-        <v>36.038937695657189</v>
-      </c>
-      <c r="I15">
-        <f t="shared" si="1"/>
-        <v>2.6445519781045606E-5</v>
-      </c>
-      <c r="J15">
-        <f t="shared" si="1"/>
-        <v>58.828985696021519</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>0.8393342017004346</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D16">
-        <f>($D$2-D4)/$D$2*100</f>
-        <v>20.783569356604197</v>
-      </c>
-      <c r="E16">
-        <f t="shared" si="1"/>
-        <v>3.0967902768175633E-2</v>
-      </c>
-      <c r="F16">
-        <f t="shared" si="1"/>
-        <v>1.2835154198101542E-2</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>4.6141031833564705</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="1"/>
-        <v>37.819374327256568</v>
-      </c>
-      <c r="I16">
-        <f t="shared" si="1"/>
-        <v>2.5175928017394161E-5</v>
-      </c>
-      <c r="J16">
-        <f t="shared" si="1"/>
-        <v>56.593897189666087</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>0.92879706682657848</v>
-      </c>
-    </row>
-    <row r="17" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D17">
-        <f>($D$2-D5)/$D$2*100</f>
-        <v>26.242618623375495</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="1"/>
-        <v>3.2578197442211486E-2</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="1"/>
-        <v>1.2938037046822878E-2</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>4.993260857590359</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="1"/>
-        <v>36.972022275117588</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="1"/>
-        <v>2.4541862427753829E-5</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="1"/>
-        <v>56.99163535287073</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>0.99754073806985133</v>
-      </c>
-    </row>
-    <row r="18" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D18">
-        <f>($D$2-D6)/$D$2*100</f>
-        <v>53.12926004799511</v>
-      </c>
-      <c r="E18">
-        <f t="shared" si="1"/>
-        <v>3.005119997980242E-2</v>
-      </c>
-      <c r="F18">
-        <f t="shared" si="1"/>
-        <v>9.2196335443378939E-3</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>4.7379993524665309</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="1"/>
-        <v>18.497596377346255</v>
-      </c>
-      <c r="I18">
-        <f t="shared" si="1"/>
-        <v>3.1188849612009727E-5</v>
-      </c>
-      <c r="J18">
-        <f t="shared" si="1"/>
-        <v>75.155337864757243</v>
-      </c>
-      <c r="K18">
-        <f t="shared" si="1"/>
-        <v>1.569764383056236</v>
-      </c>
-    </row>
-    <row r="19" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D19">
-        <f>($D$2-D7)/$D$2*100</f>
-        <v>66.632688186983586</v>
-      </c>
-      <c r="E19">
-        <f t="shared" si="1"/>
-        <v>3.4688193477825396E-2</v>
-      </c>
-      <c r="F19">
-        <f t="shared" si="1"/>
-        <v>8.1780382669359337E-3</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>5.4560724026473197</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="1"/>
-        <v>7.8656939086727657</v>
-      </c>
-      <c r="I19">
-        <f t="shared" si="1"/>
-        <v>2.0854861342659206E-5</v>
-      </c>
-      <c r="J19">
-        <f t="shared" si="1"/>
-        <v>84.430313443345653</v>
-      </c>
-      <c r="K19">
-        <f t="shared" si="1"/>
-        <v>2.2050331587281544</v>
-      </c>
-    </row>
-    <row r="20" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D20">
-        <f>($D$2-D8)/$D$2*100</f>
-        <v>70.821098626179108</v>
-      </c>
-      <c r="E20">
-        <f t="shared" si="1"/>
-        <v>3.6355203352104681E-2</v>
-      </c>
-      <c r="F20">
-        <f t="shared" si="1"/>
-        <v>7.5930210122694486E-3</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>5.7909950339157579</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="1"/>
-        <v>3.4047527149998076</v>
-      </c>
-      <c r="I20">
-        <f t="shared" si="1"/>
-        <v>1.0293142791932822E-5</v>
-      </c>
-      <c r="J20">
-        <f t="shared" si="1"/>
-        <v>88.238744643826777</v>
-      </c>
-      <c r="K20">
-        <f t="shared" si="1"/>
-        <v>2.5215490897505086</v>
-      </c>
-    </row>
-    <row r="21" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D21">
-        <f>($D$2-D9)/$D$2*100</f>
-        <v>22.410791270034956</v>
-      </c>
-      <c r="E21">
-        <f t="shared" si="1"/>
-        <v>2.9024889123116161E-2</v>
-      </c>
-      <c r="F21">
-        <f t="shared" si="1"/>
-        <v>1.1658100716535422E-2</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>4.3172921361644701</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="1"/>
-        <v>33.038398448336324</v>
-      </c>
-      <c r="I21">
-        <f t="shared" si="1"/>
-        <v>2.6439661377399548E-5</v>
-      </c>
-      <c r="J21">
-        <f t="shared" si="1"/>
-        <v>61.655323891739485</v>
-      </c>
-      <c r="K21">
-        <f t="shared" si="1"/>
-        <v>0.94827609425868697</v>
-      </c>
-    </row>
-    <row r="22" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D22">
-        <f>($D$2-D10)/$D$2*100</f>
-        <v>49.173022945789782</v>
-      </c>
-      <c r="E22">
-        <f t="shared" si="1"/>
-        <v>3.4433056126660609E-2</v>
-      </c>
-      <c r="F22">
-        <f t="shared" si="1"/>
-        <v>1.0851439263200736E-2</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>5.101980013735357</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="1"/>
-        <v>21.548170835777114</v>
-      </c>
-      <c r="I22">
-        <f t="shared" si="1"/>
-        <v>2.689043063584114E-5</v>
-      </c>
-      <c r="J22">
-        <f t="shared" si="1"/>
-        <v>71.856959751777623</v>
-      </c>
-      <c r="K22">
-        <f t="shared" si="1"/>
-        <v>1.447578012889416</v>
-      </c>
-    </row>
-    <row r="23" spans="4:11" x14ac:dyDescent="0.25">
-      <c r="D23">
-        <f>($D$2-D11)/$D$2*100</f>
-        <v>66.9634125022327</v>
-      </c>
-      <c r="E23">
-        <f t="shared" si="1"/>
-        <v>3.7040543006968421E-2</v>
-      </c>
-      <c r="F23">
-        <f t="shared" si="1"/>
-        <v>8.2511606730168788E-3</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>6.0515866917907184</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="1"/>
-        <v>5.7121753934529167</v>
-      </c>
-      <c r="I23">
-        <f t="shared" si="1"/>
-        <v>2.9434622265487161E-5</v>
-      </c>
-      <c r="J23">
-        <f t="shared" si="1"/>
-        <v>85.963809352742373</v>
-      </c>
-      <c r="K23">
-        <f t="shared" si="1"/>
-        <v>2.2271074237117174</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -511,31 +511,31 @@
         <v>2.697755753143283</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1770046506426656</v>
+        <v>0.1770046506426655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9906413026672418</v>
+        <v>0.9906413026672415</v>
       </c>
       <c r="G2" t="n">
         <v>0.03332028509091799</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00713452257158625</v>
+        <v>0.007134522571586243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007426560757672061</v>
+        <v>0.0007426560757677213</v>
       </c>
       <c r="J2" t="n">
-        <v>2.366558390921173e-05</v>
+        <v>2.366558390921154e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.05605377579863242</v>
+        <v>0.05605377579863226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002349047987132503</v>
+        <v>0.0002349047987132504</v>
       </c>
       <c r="M2" t="n">
-        <v>1.432599989913849</v>
+        <v>1.43259998991385</v>
       </c>
     </row>
     <row r="3">
@@ -553,34 +553,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.687292138134789</v>
+        <v>2.687292138134787</v>
       </c>
       <c r="E3" t="n">
         <v>0.1753652466821186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9876707119331584</v>
+        <v>0.9876707119331579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03207727081048768</v>
+        <v>0.03207727081048771</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006950845406861214</v>
+        <v>0.006950845406861197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0006728322794244151</v>
+        <v>0.0006728322794233915</v>
       </c>
       <c r="J3" t="n">
-        <v>2.292703187514307e-05</v>
+        <v>2.292703187514305e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05169753441829478</v>
+        <v>0.05169753441829477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0002347794527370766</v>
+        <v>0.0002347794527370767</v>
       </c>
       <c r="M3" t="n">
-        <v>1.432599990119831</v>
+        <v>1.432599990119832</v>
       </c>
     </row>
     <row r="4">
@@ -598,28 +598,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.681084827723791</v>
+        <v>2.681084827723792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1742297025430325</v>
+        <v>0.1742297025430326</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9855131984838942</v>
+        <v>0.9855131984838947</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03041962716113817</v>
+        <v>0.03041962716113819</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006725871138007349</v>
+        <v>0.006725871138007345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006432079368328305</v>
+        <v>0.0006432079368332881</v>
       </c>
       <c r="J4" t="n">
         <v>2.238978961716149e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05069627631781798</v>
+        <v>0.05069627631781801</v>
       </c>
       <c r="L4" t="n">
         <v>0.0002345640871387253</v>
@@ -643,34 +643,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.674903125675852</v>
+        <v>2.67490312567585</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909714</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9826184071732463</v>
+        <v>0.9826184071732462</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02768872593440491</v>
+        <v>0.02768872593440493</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00659710353478249</v>
+        <v>0.0065971035347825</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0005832603437579099</v>
+        <v>0.0005832603437575347</v>
       </c>
       <c r="J5" t="n">
         <v>2.221023784335879e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05108145198441414</v>
+        <v>0.05108145198441418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0002344813412966111</v>
+        <v>0.0002344813412966112</v>
       </c>
       <c r="M5" t="n">
-        <v>1.432599990435135</v>
+        <v>1.432599990435133</v>
       </c>
     </row>
     <row r="6">
@@ -694,22 +694,22 @@
         <v>0.1654487886793511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9685272857894485</v>
+        <v>0.9685272857894489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008803216561351725</v>
+        <v>0.008803216561351732</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005755797827749527</v>
+        <v>0.005755797827749523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0002593664518786093</v>
+        <v>0.0002593664518788263</v>
       </c>
       <c r="J6" t="n">
-        <v>1.970247582360309e-05</v>
+        <v>1.970247582360287e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03080138859357328</v>
+        <v>0.03080138859357326</v>
       </c>
       <c r="L6" t="n">
         <v>0.0002343257814860046</v>
@@ -739,25 +739,25 @@
         <v>0.1615019614938296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9625373585235346</v>
+        <v>0.9625373585235352</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002664909953161948</v>
+        <v>0.002664909953161934</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005183495819838611</v>
+        <v>0.0051834958198386</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0001351527580923563</v>
+        <v>0.0001351527580920203</v>
       </c>
       <c r="J7" t="n">
-        <v>1.837741014355899e-05</v>
+        <v>1.837741014355898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02525078206769129</v>
+        <v>0.02525078206769121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002339038671066824</v>
+        <v>0.0002339038671066825</v>
       </c>
       <c r="M7" t="n">
         <v>1.43259999228663</v>
@@ -781,28 +781,28 @@
         <v>2.581879576756648</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1600401217258295</v>
+        <v>0.1600401217258294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9594933224300903</v>
+        <v>0.9594933224300902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001008738944661727</v>
+        <v>0.001008738944661732</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004997759118034207</v>
+        <v>0.004997759118034205</v>
       </c>
       <c r="I8" t="n">
-        <v>5.141759203971353e-05</v>
+        <v>5.141759203929287e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>1.784742985847452e-05</v>
+        <v>1.784742985847448e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02343665449195837</v>
+        <v>0.02343665449195834</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002337225489288063</v>
+        <v>0.0002337225489288064</v>
       </c>
       <c r="M8" t="n">
         <v>1.432599992475247</v>
@@ -823,34 +823,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2.66693876755419</v>
+        <v>2.666938767554188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1724597851737663</v>
+        <v>0.1724597851737662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9820751158796153</v>
+        <v>0.982075115879616</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02602822705092954</v>
+        <v>0.02602822705092955</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006535004021761015</v>
+        <v>0.006535004021761018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005231448288669495</v>
+        <v>0.0005231448288676976</v>
       </c>
       <c r="J9" t="n">
-        <v>2.211240974831635e-05</v>
+        <v>2.211240974831638e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04646075348385699</v>
+        <v>0.046460753483857</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0002346341295683079</v>
+        <v>0.000234634129568308</v>
       </c>
       <c r="M9" t="n">
-        <v>1.432599990576077</v>
+        <v>1.432599990576074</v>
       </c>
     </row>
     <row r="10">
@@ -871,28 +871,28 @@
         <v>2.625473643986356</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1666093608370145</v>
+        <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9727659338281379</v>
+        <v>0.9727659338281373</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01112061915572759</v>
+        <v>0.01112061915572761</v>
       </c>
       <c r="H10" t="n">
-        <v>0.005847858327735188</v>
+        <v>0.005847858327735178</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0003082891040218321</v>
+        <v>0.0003082891040219593</v>
       </c>
       <c r="J10" t="n">
-        <v>2.015830940726058e-05</v>
+        <v>2.015830940726041e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03596719112729569</v>
+        <v>0.03596719112729567</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002342417742032933</v>
+        <v>0.0002342417742032932</v>
       </c>
       <c r="M10" t="n">
         <v>1.432599991522813</v>
@@ -913,34 +913,34 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2.595516863958471</v>
+        <v>2.595516863958469</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1627298041679663</v>
+        <v>0.1627298041679664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.964672581026609</v>
+        <v>0.9646725810266094</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001916112446268605</v>
+        <v>0.001916112446268601</v>
       </c>
       <c r="H11" t="n">
-        <v>0.005419358970709856</v>
+        <v>0.005419358970709857</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001967717792876397</v>
+        <v>0.0001967717792864079</v>
       </c>
       <c r="J11" t="n">
-        <v>1.89550840178838e-05</v>
+        <v>1.895508401788377e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02772923758671251</v>
+        <v>0.02772923758671249</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002340507071139728</v>
+        <v>0.0002340507071139727</v>
       </c>
       <c r="M11" t="n">
-        <v>1.432599992189785</v>
+        <v>1.432599992189784</v>
       </c>
     </row>
   </sheetData>
@@ -985,37 +985,37 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>carbon dioxide capture, chemical absorption, with transport and storage, 200 km pipeline sotage 1000m</t>
+          <t>market group for electricity, high voltage</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>market group for electricity, high voltage</t>
+          <t>market for nickel, class 1</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
+          <t>market for tap water</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>market for tap water</t>
+          <t>market for solvent, organic</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>market for solvent, organic</t>
+          <t>market for chemical factory, organics</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>market for chemical factory, organics</t>
+          <t>market for municipal solid waste</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>market for municipal solid waste</t>
+          <t>carbon dioxide storage from natural gas, post, 200km pipeline, storage 1000m</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -1039,37 +1039,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.298036154075481</v>
+        <v>0.9246210070061189</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1770046506426656</v>
+        <v>0.1770046506426655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4884743561724417</v>
+        <v>0.3708568020944534</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3890983301763351</v>
+        <v>0.160723838701418</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1743984867889448</v>
+        <v>0.007134522571586243</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00713452257158625</v>
+        <v>0.0007426560757677213</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0007426560757672061</v>
+        <v>2.366558390921154e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>2.366558390921173e-05</v>
+        <v>0.05605377579863226</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05605377579863242</v>
+        <v>0.0002349047987132504</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0002349047987132503</v>
+        <v>0.008586208395600771</v>
       </c>
       <c r="N2" t="n">
-        <v>0.004870805466484995</v>
+        <v>0.1432599823433726</v>
       </c>
     </row>
     <row r="3">
@@ -1087,37 +1087,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.260602839616695</v>
+        <v>0.9056681866039387</v>
       </c>
       <c r="E3" t="n">
         <v>0.1753652466821186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4781000183790347</v>
+        <v>0.3644746828538878</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3747953037896375</v>
+        <v>0.154728030857448</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1678925457691552</v>
+        <v>0.006950845406861197</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006950845406861214</v>
+        <v>0.0006728322794233915</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0006728322794244151</v>
+        <v>2.292703187514305e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>2.292703187514307e-05</v>
+        <v>0.05169753441829477</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05169753441829478</v>
+        <v>0.0002347794527370767</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002347794527370766</v>
+        <v>0.008261324868433024</v>
       </c>
       <c r="N3" t="n">
-        <v>0.004870806407556438</v>
+        <v>0.1432599827528597</v>
       </c>
     </row>
     <row r="4">
@@ -1135,37 +1135,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.218161368648327</v>
+        <v>0.8875706696859518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1742297025430325</v>
+        <v>0.1742297025430326</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4657699440130857</v>
+        <v>0.3572008492456238</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3557521720758192</v>
+        <v>0.1467322154016225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1592164332061014</v>
+        <v>0.006725871138007345</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006725871138007349</v>
+        <v>0.0006432079368332881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006432079368328305</v>
+        <v>2.238978961716149e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>2.238978961716149e-05</v>
+        <v>0.05069627631781801</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05069627631781798</v>
+        <v>0.0002345640871387253</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0002345640871387253</v>
+        <v>0.007825610041921354</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0048708075408741</v>
+        <v>0.1432599831843367</v>
       </c>
     </row>
     <row r="5">
@@ -1183,37 +1183,37 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.153485059498486</v>
+        <v>0.8627179081859904</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1734774946909714</v>
+        <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.447322709927681</v>
+        <v>0.3467778446910367</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3243726513401715</v>
+        <v>0.1335594311028888</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1449228867909727</v>
+        <v>0.0065971035347825</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00659710353478249</v>
+        <v>0.0005832603437575347</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0005832603437579099</v>
+        <v>2.221023784335879e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>2.221023784335879e-05</v>
+        <v>0.05108145198441418</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05108145198441414</v>
+        <v>0.0002344813412966112</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002344813412966111</v>
+        <v>0.007124646457739239</v>
       </c>
       <c r="N5" t="n">
-        <v>0.004870809306595003</v>
+        <v>0.1432599838012601</v>
       </c>
     </row>
     <row r="6">
@@ -1231,37 +1231,37 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6766768460472113</v>
+        <v>0.6755548112951671</v>
       </c>
       <c r="E6" t="n">
         <v>0.1654487886793511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.318289697332108</v>
+        <v>0.2850078986977806</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1049208912145613</v>
+        <v>0.04246322487336681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04607606576552317</v>
+        <v>0.005755797827749523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.005755797827749527</v>
+        <v>0.0002593664518788263</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0002593664518786093</v>
+        <v>1.970247582360287e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>1.970247582360309e-05</v>
+        <v>0.03080138859357326</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03080138859357328</v>
+        <v>0.0002343257814860046</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0002343257814860046</v>
+        <v>0.002304329773415939</v>
       </c>
       <c r="N6" t="n">
-        <v>0.004870821925156643</v>
+        <v>0.1432599881407414</v>
       </c>
     </row>
     <row r="7">
@@ -1279,37 +1279,37 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5183808261049229</v>
+        <v>0.611772672780345</v>
       </c>
       <c r="E7" t="n">
         <v>0.1615019614938296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2737136580673183</v>
+        <v>0.262628182872136</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03352452063276107</v>
+        <v>0.01285446857063499</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01394814786224369</v>
+        <v>0.0051834958198386</v>
       </c>
       <c r="I7" t="n">
-        <v>0.005183495819838611</v>
+        <v>0.0001351527580920203</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001351527580923563</v>
+        <v>1.837741014355898e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>1.837741014355899e-05</v>
+        <v>0.02525078206769121</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02525078206769129</v>
+        <v>0.0002339038671066825</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0002339038671066824</v>
+        <v>0.0007063582802680504</v>
       </c>
       <c r="N7" t="n">
-        <v>0.004870826125897731</v>
+        <v>0.1432599896406043</v>
       </c>
     </row>
     <row r="8">
@@ -1327,37 +1327,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4740561710356407</v>
+        <v>0.593273063067533</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1600401217258295</v>
+        <v>0.1600401217258294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2607387741412048</v>
+        <v>0.2561094575310152</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01438930358414369</v>
+        <v>0.004865756550139483</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005279743106460837</v>
+        <v>0.004997759118034205</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004997759118034207</v>
+        <v>5.141759203929287e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>5.141759203971353e-05</v>
+        <v>1.784742985847448e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>1.784742985847452e-05</v>
+        <v>0.02343665449195834</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02343665449195837</v>
+        <v>0.0002337225489288064</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002337225489288063</v>
+        <v>0.0002603360053185242</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004870827297182356</v>
+        <v>0.1432599900744113</v>
       </c>
     </row>
     <row r="9">
@@ -1375,37 +1375,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.107090295350969</v>
+        <v>0.8420136194555626</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1724597851737663</v>
+        <v>0.1724597851737662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4351967289914461</v>
+        <v>0.3402601737709401</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3045554919040149</v>
+        <v>0.1255498431301756</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1362318299226812</v>
+        <v>0.006535004021761018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.006535004021761015</v>
+        <v>0.0005231448288676976</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0005231448288669495</v>
+        <v>2.211240974831638e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>2.211240974831635e-05</v>
+        <v>0.046460753483857</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04646075348385699</v>
+        <v>0.000234634129568308</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0002346341295683079</v>
+        <v>0.006708184258463761</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004870810485259502</v>
+        <v>0.1432599842484145</v>
       </c>
     </row>
     <row r="10">
@@ -1423,37 +1423,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.7367516967003087</v>
+        <v>0.6996346860311687</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1666093608370145</v>
+        <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3333468587062501</v>
+        <v>0.2908506117821993</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1313415592242791</v>
+        <v>0.05364145578490961</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05820535891644178</v>
+        <v>0.005847858327735178</v>
       </c>
       <c r="I10" t="n">
-        <v>0.005847858327735188</v>
+        <v>0.0003082891040219593</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0003082891040218321</v>
+        <v>2.015830940726041e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>2.015830940726058e-05</v>
+        <v>0.03596719112729567</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03596719112729569</v>
+        <v>0.0002342417742032932</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0002342417742032933</v>
+        <v>0.002895531366861593</v>
       </c>
       <c r="N10" t="n">
-        <v>0.004870820373659934</v>
+        <v>0.1432599876175202</v>
       </c>
     </row>
     <row r="11">
@@ -1471,37 +1471,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5081867562328466</v>
+        <v>0.6132698394333544</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1627298041679663</v>
+        <v>0.1627298041679664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2720540223930645</v>
+        <v>0.2638856862510028</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02490478995275835</v>
+        <v>0.009242566409847306</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01002893913527148</v>
+        <v>0.005419358970709857</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005419358970709856</v>
+        <v>0.0001967717792864079</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0001967717792876397</v>
+        <v>1.895508401788377e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>1.89550840178838e-05</v>
+        <v>0.02772923758671249</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02772923758671251</v>
+        <v>0.0002340507071139727</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002340507071139728</v>
+        <v>0.0005534188380350803</v>
       </c>
       <c r="N11" t="n">
-        <v>0.004870826455944055</v>
+        <v>0.1432599896386622</v>
       </c>
     </row>
   </sheetData>
@@ -1585,28 +1585,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8537556471123272</v>
+        <v>0.8537556471123267</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003092361873368601</v>
+        <v>0.0003092361873368595</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001274586581092433</v>
+        <v>0.0001274586581092432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04634287500342422</v>
+        <v>0.04634287500342413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3763015622064995</v>
+        <v>0.3763015622064994</v>
       </c>
       <c r="I2" t="n">
-        <v>2.871800364506607e-07</v>
+        <v>2.871800364506604e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4222372346777831</v>
+        <v>0.4222372346777827</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436993199137821</v>
+        <v>0.008436993199137932</v>
       </c>
     </row>
     <row r="3">
@@ -1624,28 +1624,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.7925894383766177</v>
+        <v>0.7925894383766169</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002878884378641579</v>
+        <v>0.0002878884378641581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001211983546970559</v>
+        <v>0.000121198354697056</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04274132012335734</v>
+        <v>0.04274132012335746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3622636206254294</v>
+        <v>0.3622636206254295</v>
       </c>
       <c r="I3" t="n">
-        <v>2.658305254751741e-07</v>
+        <v>2.658305254751853e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3787381513588898</v>
+        <v>0.3787381513588894</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436993645854374</v>
+        <v>0.008436993645853819</v>
       </c>
     </row>
     <row r="4">
@@ -1663,28 +1663,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7358395778613148</v>
+        <v>0.7358395778613149</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045907</v>
+        <v>0.0002813057792045911</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047333</v>
+        <v>0.04191352256047336</v>
       </c>
       <c r="H4" t="n">
         <v>0.3435430756742119</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425427e-07</v>
+        <v>2.28692724242526e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3415478593147125</v>
+        <v>0.3415478593147124</v>
       </c>
       <c r="K4" t="n">
-        <v>0.008436994055263991</v>
+        <v>0.008436994055264213</v>
       </c>
     </row>
     <row r="5">
@@ -1702,28 +1702,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6976469345594682</v>
+        <v>0.6976469345594712</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002755396677122547</v>
+        <v>0.0002755396677122548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000109427246091625</v>
+        <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044276</v>
+        <v>0.04223196940044275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784109</v>
+        <v>0.312701730978411</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810017e-07</v>
+        <v>2.075700053810025e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3338910652886797</v>
+        <v>0.3338910652886807</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436994408125509</v>
+        <v>0.008436994408127618</v>
       </c>
     </row>
     <row r="6">
@@ -1741,28 +1741,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4042680512618921</v>
+        <v>0.4042680512618917</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001615158763762973</v>
+        <v>0.0001615158763762972</v>
       </c>
       <c r="F6" t="n">
-        <v>4.955266986951889e-05</v>
+        <v>4.955266986951887e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02546527653465744</v>
+        <v>0.0254652765346574</v>
       </c>
       <c r="H6" t="n">
         <v>0.09941884156872663</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67630390188632e-07</v>
+        <v>1.676303901886094e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2707356997273897</v>
+        <v>0.2707356997273895</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436997254482326</v>
+        <v>0.008436997254482215</v>
       </c>
     </row>
     <row r="7">
@@ -1780,28 +1780,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.276935512004123</v>
+        <v>0.2769355120041219</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001327255374027538</v>
+        <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
-        <v>3.129118051573439e-05</v>
+        <v>3.129118051573435e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02087627140953946</v>
+        <v>0.02087627140953941</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03009607438166334</v>
+        <v>0.03009607438166322</v>
       </c>
       <c r="I7" t="n">
-        <v>7.979581528031622e-08</v>
+        <v>7.979581528031568e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2173620713574989</v>
+        <v>0.2173620713574962</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436998341687596</v>
+        <v>0.008436998341689261</v>
       </c>
     </row>
     <row r="8">
@@ -1819,28 +1819,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.2424674618526512</v>
+        <v>0.2424674618526509</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000121642994895939</v>
+        <v>0.0001216429948959389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.540593178078808e-05</v>
+        <v>2.540593178078807e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01937642797732396</v>
+        <v>0.01937642797732395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139216065225714</v>
+        <v>0.01139216065225715</v>
       </c>
       <c r="I8" t="n">
-        <v>3.44404266969881e-08</v>
+        <v>3.444042669698776e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2031147912169413</v>
+        <v>0.2031147912169405</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998639025389</v>
+        <v>0.008436998639025944</v>
       </c>
     </row>
     <row r="9">
@@ -1858,28 +1858,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.685795029435511</v>
+        <v>0.6857950294355116</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002582399815828585</v>
+        <v>0.0002582399815828589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001037243484913611</v>
+        <v>0.0001037243484913613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03841177263423207</v>
+        <v>0.038411772634232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2939489405329221</v>
+        <v>0.2939489405329222</v>
       </c>
       <c r="I9" t="n">
-        <v>2.352387166130069e-07</v>
+        <v>2.352387166130072e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3446351220860785</v>
+        <v>0.3446351220860783</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436994613487458</v>
+        <v>0.008436994613488236</v>
       </c>
     </row>
     <row r="10">
@@ -1897,28 +1897,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4317308177176369</v>
+        <v>0.4317308177176362</v>
       </c>
       <c r="E10" t="n">
         <v>0.0002006880166748545</v>
       </c>
       <c r="F10" t="n">
-        <v>6.324602195601289e-05</v>
+        <v>6.324602195601288e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0297361421044039</v>
+        <v>0.02973614210440392</v>
       </c>
       <c r="H10" t="n">
         <v>0.1255903528311779</v>
       </c>
       <c r="I10" t="n">
-        <v>1.567269304237355e-07</v>
+        <v>1.567269304237346e-07</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2677032350937334</v>
+        <v>0.2677032350937337</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436996922760398</v>
+        <v>0.008436996922759454</v>
       </c>
     </row>
     <row r="11">
@@ -1936,28 +1936,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.285898051371327</v>
+        <v>0.2858980513713277</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001403214666166647</v>
+        <v>0.0001403214666166644</v>
       </c>
       <c r="F11" t="n">
-        <v>3.125804518334548e-05</v>
+        <v>3.12580451833455e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02292535289750498</v>
+        <v>0.02292535289750495</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02163955395119726</v>
+        <v>0.0216395539511973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.115077974107053e-07</v>
+        <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.232724455195474</v>
+        <v>0.2327244551954738</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00843699830755329</v>
+        <v>0.008436998307554233</v>
       </c>
     </row>
   </sheetData>
@@ -2041,28 +2041,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.146704692771252</v>
+        <v>1.146704692771251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0003092361873368601</v>
+        <v>0.0003092361873368595</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0001274586581092433</v>
+        <v>0.0001274586581092432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04634287500342422</v>
+        <v>0.04634287500342413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3763015622064995</v>
+        <v>0.3763015622064994</v>
       </c>
       <c r="I2" t="n">
-        <v>2.871800364506607e-07</v>
+        <v>2.871800364506604e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7151862819240827</v>
+        <v>0.7151862819240824</v>
       </c>
       <c r="K2" t="n">
-        <v>0.008436991611762812</v>
+        <v>0.008436991611761924</v>
       </c>
     </row>
     <row r="3">
@@ -2080,28 +2080,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.005200607422688</v>
+        <v>1.005200607422686</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0002878884378641579</v>
+        <v>0.0002878884378641581</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001211983546970559</v>
+        <v>0.000121198354697056</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04274132012335734</v>
+        <v>0.04274132012335746</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3622636206254294</v>
+        <v>0.3622636206254295</v>
       </c>
       <c r="I3" t="n">
-        <v>2.658305254751741e-07</v>
+        <v>2.658305254751853e-07</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5913493215570141</v>
+        <v>0.5913493215570148</v>
       </c>
       <c r="K3" t="n">
-        <v>0.008436992493800033</v>
+        <v>0.008436992493797257</v>
       </c>
     </row>
     <row r="4">
@@ -2119,25 +2119,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9083785276337039</v>
+        <v>0.9083785276337035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0002813057792045907</v>
+        <v>0.0002813057792045911</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001165917847242302</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04191352256047333</v>
+        <v>0.04191352256047336</v>
       </c>
       <c r="H4" t="n">
         <v>0.3435430756742119</v>
       </c>
       <c r="I4" t="n">
-        <v>2.286927242425427e-07</v>
+        <v>2.28692724242526e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5140868100220204</v>
+        <v>0.5140868100220201</v>
       </c>
       <c r="K4" t="n">
         <v>0.008436993120345071</v>
@@ -2158,28 +2158,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8457793535109427</v>
+        <v>0.845779353510943</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0002755396677122547</v>
+        <v>0.0002755396677122548</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000109427246091625</v>
+        <v>0.0001094272460916249</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04223196940044276</v>
+        <v>0.04223196940044275</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3127017309784109</v>
+        <v>0.312701730978411</v>
       </c>
       <c r="I5" t="n">
-        <v>2.075700053810017e-07</v>
+        <v>2.075700053810025e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4820234850428242</v>
+        <v>0.482023485042825</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008436993605455578</v>
+        <v>0.008436993605455023</v>
       </c>
     </row>
     <row r="6">
@@ -2200,25 +2200,25 @@
         <v>0.5374689745662495</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001615158763762973</v>
+        <v>0.0001615158763762972</v>
       </c>
       <c r="F6" t="n">
-        <v>4.955266986951889e-05</v>
+        <v>4.955266986951887e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02546527653465744</v>
+        <v>0.0254652765346574</v>
       </c>
       <c r="H6" t="n">
         <v>0.09941884156872663</v>
       </c>
       <c r="I6" t="n">
-        <v>1.67630390188632e-07</v>
+        <v>1.676303901886094e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4039366237535118</v>
+        <v>0.4039366237535108</v>
       </c>
       <c r="K6" t="n">
-        <v>0.008436996532717678</v>
+        <v>0.008436996532718677</v>
       </c>
     </row>
     <row r="7">
@@ -2236,28 +2236,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.3826245304114769</v>
+        <v>0.3826245304114756</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001327255374027538</v>
+        <v>0.0001327255374027534</v>
       </c>
       <c r="F7" t="n">
-        <v>3.129118051573439e-05</v>
+        <v>3.129118051573435e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02087627140953946</v>
+        <v>0.02087627140953941</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03009607438166334</v>
+        <v>0.03009607438166322</v>
       </c>
       <c r="I7" t="n">
-        <v>7.979581528031622e-08</v>
+        <v>7.979581528031568e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3230510903375391</v>
+        <v>0.3230510903375375</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008436997769001198</v>
+        <v>0.008436997769001697</v>
       </c>
     </row>
     <row r="8">
@@ -2275,28 +2275,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3345958313527</v>
+        <v>0.3345958313526997</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000121642994895939</v>
+        <v>0.0001216429948959389</v>
       </c>
       <c r="F8" t="n">
-        <v>2.540593178078808e-05</v>
+        <v>2.540593178078807e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01937642797732396</v>
+        <v>0.01937642797732395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01139216065225714</v>
+        <v>0.01139216065225715</v>
       </c>
       <c r="I8" t="n">
-        <v>3.44404266969881e-08</v>
+        <v>3.444042669698776e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2952431612161977</v>
+        <v>0.2952431612161971</v>
       </c>
       <c r="K8" t="n">
-        <v>0.008436998139817742</v>
+        <v>0.008436998139817964</v>
       </c>
     </row>
     <row r="9">
@@ -2314,28 +2314,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8897190975905902</v>
+        <v>0.889719097590591</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0002582399815828585</v>
+        <v>0.0002582399815828589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0001037243484913611</v>
+        <v>0.0001037243484913613</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03841177263423207</v>
+        <v>0.038411772634232</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2939489405329221</v>
+        <v>0.2939489405329222</v>
       </c>
       <c r="I9" t="n">
-        <v>2.352387166130069e-07</v>
+        <v>2.352387166130072e-07</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5485591913461405</v>
+        <v>0.5485591913461414</v>
       </c>
       <c r="K9" t="n">
-        <v>0.008436993508504687</v>
+        <v>0.008436993508504576</v>
       </c>
     </row>
     <row r="10">
@@ -2353,28 +2353,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.5828353310743943</v>
+        <v>0.5828353310743946</v>
       </c>
       <c r="E10" t="n">
         <v>0.0002006880166748545</v>
       </c>
       <c r="F10" t="n">
-        <v>6.324602195601289e-05</v>
+        <v>6.324602195601288e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0297361421044039</v>
+        <v>0.02973614210440392</v>
       </c>
       <c r="H10" t="n">
         <v>0.1255903528311779</v>
       </c>
       <c r="I10" t="n">
-        <v>1.567269304237355e-07</v>
+        <v>1.567269304237346e-07</v>
       </c>
       <c r="J10" t="n">
         <v>0.4188077492692669</v>
       </c>
       <c r="K10" t="n">
-        <v>0.008436996103984296</v>
+        <v>0.008436996103984518</v>
       </c>
     </row>
     <row r="11">
@@ -2392,28 +2392,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.378832099168379</v>
+        <v>0.3788320991683785</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0001403214666166647</v>
+        <v>0.0001403214666166644</v>
       </c>
       <c r="F11" t="n">
-        <v>3.125804518334548e-05</v>
+        <v>3.12580451833455e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02292535289750498</v>
+        <v>0.02292535289750495</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02163955395119726</v>
+        <v>0.0216395539511973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.115077974107053e-07</v>
+        <v>1.115077974106278e-07</v>
       </c>
       <c r="J11" t="n">
-        <v>0.325658503496096</v>
+        <v>0.325658503496097</v>
       </c>
       <c r="K11" t="n">
-        <v>0.008436997803983326</v>
+        <v>0.008436997803981772</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia climate change breakdown results.xlsx
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9246210070061189</v>
+        <v>0.8454435292966879</v>
       </c>
       <c r="E2" t="n">
         <v>0.1770046506426655</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3708568020944534</v>
+        <v>0.2916793224799666</v>
       </c>
       <c r="G2" t="n">
         <v>0.160723838701418</v>
@@ -1069,7 +1069,7 @@
         <v>0.008586208395600771</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1432599823433726</v>
+        <v>0.1432599842484283</v>
       </c>
     </row>
     <row r="3">
@@ -1087,13 +1087,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9056681866039387</v>
+        <v>0.8297272256745353</v>
       </c>
       <c r="E3" t="n">
         <v>0.1753652466821186</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3644746828538878</v>
+        <v>0.2885337200973004</v>
       </c>
       <c r="G3" t="n">
         <v>0.154728030857448</v>
@@ -1117,7 +1117,7 @@
         <v>0.008261324868433024</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1432599827528597</v>
+        <v>0.1432599845800437</v>
       </c>
     </row>
     <row r="4">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8875706696859518</v>
+        <v>0.8161960320169334</v>
       </c>
       <c r="E4" t="n">
         <v>0.1742297025430326</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3572008492456238</v>
+        <v>0.2858262098592902</v>
       </c>
       <c r="G4" t="n">
         <v>0.1467322154016225</v>
@@ -1165,7 +1165,7 @@
         <v>0.007825610041921354</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1432599831843367</v>
+        <v>0.143259984901652</v>
       </c>
     </row>
     <row r="5">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8627179081859904</v>
+        <v>0.7991849942674052</v>
       </c>
       <c r="E5" t="n">
         <v>0.1734774946909713</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3467778446910367</v>
+        <v>0.2832449292438119</v>
       </c>
       <c r="G5" t="n">
         <v>0.1335594311028888</v>
@@ -1213,7 +1213,7 @@
         <v>0.007124646457739239</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1432599838012601</v>
+        <v>0.1432599853298997</v>
       </c>
     </row>
     <row r="6">
@@ -1231,13 +1231,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.6755548112951671</v>
+        <v>0.6557639005604456</v>
       </c>
       <c r="E6" t="n">
         <v>0.1654487886793511</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2850078986977806</v>
+        <v>0.2652169874868783</v>
       </c>
       <c r="G6" t="n">
         <v>0.04246322487336681</v>
@@ -1261,7 +1261,7 @@
         <v>0.002304329773415939</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1432599881407414</v>
+        <v>0.1432599886169221</v>
       </c>
     </row>
     <row r="7">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.611772672780345</v>
+        <v>0.6058827270538962</v>
       </c>
       <c r="E7" t="n">
         <v>0.1615019614938296</v>
       </c>
       <c r="F7" t="n">
-        <v>0.262628182872136</v>
+        <v>0.2567382370039719</v>
       </c>
       <c r="G7" t="n">
         <v>0.01285446857063499</v>
@@ -1309,7 +1309,7 @@
         <v>0.0007063582802680504</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1432599896406043</v>
+        <v>0.1432599897823197</v>
       </c>
     </row>
     <row r="8">
@@ -1327,13 +1327,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.593273063067533</v>
+        <v>0.5905913461131849</v>
       </c>
       <c r="E8" t="n">
         <v>0.1600401217258294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2561094575310152</v>
+        <v>0.2534277405121432</v>
       </c>
       <c r="G8" t="n">
         <v>0.004865756550139483</v>
@@ -1357,7 +1357,7 @@
         <v>0.0002603360053185242</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1432599900744113</v>
+        <v>0.1432599901389351</v>
       </c>
     </row>
     <row r="9">
@@ -1375,13 +1375,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8420136194555626</v>
+        <v>0.7829072981714438</v>
       </c>
       <c r="E9" t="n">
         <v>0.1724597851737662</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3402601737709401</v>
+        <v>0.281153851064688</v>
       </c>
       <c r="G9" t="n">
         <v>0.1255498431301756</v>
@@ -1405,7 +1405,7 @@
         <v>0.006708184258463761</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1432599842484145</v>
+        <v>0.1432599856705479</v>
       </c>
     </row>
     <row r="10">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.6996346860311687</v>
+        <v>0.6757001199580152</v>
       </c>
       <c r="E10" t="n">
         <v>0.1666093608370146</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2908506117821993</v>
+        <v>0.2669160451331652</v>
       </c>
       <c r="G10" t="n">
         <v>0.05364145578490961</v>
@@ -1453,7 +1453,7 @@
         <v>0.002895531366861593</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1432599876175202</v>
+        <v>0.1432599881934007</v>
       </c>
     </row>
     <row r="11">
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.6132698394333544</v>
+        <v>0.608843758446703</v>
       </c>
       <c r="E11" t="n">
         <v>0.1627298041679664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2638856862510028</v>
+        <v>0.259459605157857</v>
       </c>
       <c r="G11" t="n">
         <v>0.009242566409847306</v>
@@ -1501,7 +1501,7 @@
         <v>0.0005534188380350803</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1432599896386622</v>
+        <v>0.1432599897451566</v>
       </c>
     </row>
   </sheetData>
